--- a/UAT_Excel_Reports/Wba Alerts_UAT.xlsx
+++ b/UAT_Excel_Reports/Wba Alerts_UAT.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F196"/>
+  <dimension ref="A1:F178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -496,26 +496,39 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>--- NAVIGATION TO DASHBOARD ---</t>
-        </is>
-      </c>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>D.1</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Open the Executive Dashboard page by navigating to the specified URL.</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>`page.goto("https://stage.wba.esp.antuit.ai/dp/demand-planning/executive-dashboard?workbookId=6&amp;tabIndex=1")`</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>D.1</t>
+          <t>E.1</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Open the Executive Dashboard page by navigating to the specified URL.</t>
+          <t>Click on the 'Alerts' filter dropdown to expand the filter options.</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>`page.goto("https://stage.wba.esp.antuit.ai/dp/demand-planning/executive-dashboard?workbookId=6&amp;tabIndex=1")`</t>
+          <t>`page.locator("#alerts-filterId").click()`</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
@@ -523,26 +536,39 @@
       <c r="F4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>--- ALERTS FILTER INTERACTION ---</t>
-        </is>
-      </c>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>E.2</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>From the dropdown list, select the 'MAPE' option to apply the filter.</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^MAPE$")).nth(1).click()`</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>E.1</t>
+          <t>E.3</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Alerts' filter dropdown to expand the filter options.</t>
+          <t>Click on the dropdown caret to open the filter options again.</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#alerts-filterId").click()`</t>
+          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
@@ -552,17 +578,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>E.2</t>
+          <t>E.4</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>From the dropdown list, select the 'MAPE' option to apply the filter.</t>
+          <t>From the dropdown list, select the 'Under Bias' option to apply the filter.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^MAPE$")).nth(1).click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Under Bias$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
@@ -572,7 +598,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>E.3</t>
+          <t>E.5</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -592,17 +618,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>E.4</t>
+          <t>E.6</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>From the dropdown list, select the 'Under Bias' option to apply the filter.</t>
+          <t>From the dropdown list, select the 'Over Bias' option to apply the filter.</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Under Bias$")).nth(1).click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Over Bias$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
@@ -612,7 +638,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>E.5</t>
+          <t>E.7</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -632,17 +658,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>E.6</t>
+          <t>E.8</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>From the dropdown list, select the 'Over Bias' option to apply the filter.</t>
+          <t>From the dropdown list, select the 'PVA' option to apply the filter.</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Over Bias$")).nth(1).click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^PVA$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr"/>
@@ -652,7 +678,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>E.7</t>
+          <t>E.9</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -672,17 +698,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>E.8</t>
+          <t>E.10</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>From the dropdown list, select the 'PVA' option to apply the filter.</t>
+          <t>From the dropdown list, select the 'SSIS' option to apply the filter.</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^PVA$")).nth(1).click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^SSIS$")).first.click()`</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -692,17 +718,17 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>E.9</t>
+          <t>F.1</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret to open the filter options again.</t>
+          <t>Click on the 'Columns' button to open the column visibility configuration panel.</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.get_by_role("button", name="columns").click()`</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr"/>
@@ -712,17 +738,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>E.10</t>
+          <t>F.2</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>From the dropdown list, select the 'SSIS' option to apply the filter.</t>
+          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to hide all columns initially.</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^SSIS$")).first.click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr"/>
@@ -730,26 +756,39 @@
       <c r="F15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>--- COLUMN VISIBILITY CONFIGURATION ---</t>
-        </is>
-      </c>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>F.3</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Check the 'Store Count Column' checkbox to make the 'Store Count' column visible.</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("treeitem", name="Store Count Column").get_by_label("Press SPACE to toggle").check()`</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>F.1</t>
+          <t>F.4</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Columns' button to open the column visibility configuration panel.</t>
+          <t>Check the 'Product Count Column' checkbox to make the 'Product Count' column visible.</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="columns").click()`</t>
+          <t>`page.get_by_role("treeitem", name="Product Count Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr"/>
@@ -759,17 +798,17 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>F.2</t>
+          <t>F.5</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to hide all columns initially.</t>
+          <t>Check the 'Stability Column' checkbox to make the 'Stability' column visible.</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
+          <t>`page.get_by_role("treeitem", name="Stability Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr"/>
@@ -779,17 +818,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>F.3</t>
+          <t>F.6</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Store Count Column' checkbox to make the 'Store Count' column visible.</t>
+          <t>Check the 'SSIS Column' checkbox to make the 'SSIS' column visible.</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Store Count Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_role("treeitem", name="SSIS Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr"/>
@@ -799,17 +838,17 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>F.4</t>
+          <t>F.7</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Product Count Column' checkbox to make the 'Product Count' column visible.</t>
+          <t>Check the 'User Bias Column' checkbox to make the 'User Bias' column visible.</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Product Count Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_role("treeitem", name="User Bias Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr"/>
@@ -819,17 +858,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>F.5</t>
+          <t>F.8</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Stability Column' checkbox to make the 'Stability' column visible.</t>
+          <t>Check the 'System Bias Column' checkbox to make the 'System Bias' column visible.</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Stability Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_role("treeitem", name="System Bias Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
@@ -839,17 +878,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>F.6</t>
+          <t>F.9</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Check the 'SSIS Column' checkbox to make the 'SSIS' column visible.</t>
+          <t>Check the 'User MAPE Column' checkbox to make the 'User MAPE' column visible.</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="SSIS Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_role("treeitem", name="User MAPE Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
@@ -859,17 +898,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>F.7</t>
+          <t>F.10</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Check the 'User Bias Column' checkbox to make the 'User Bias' column visible.</t>
+          <t>Check the 'System MAPE Column' checkbox to make the 'System MAPE' column visible.</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="User Bias Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_role("treeitem", name="System MAPE Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr"/>
@@ -879,17 +918,17 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>F.8</t>
+          <t>F.11</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Check the 'System Bias Column' checkbox to make the 'System Bias' column visible.</t>
+          <t>Check the 'Planner Value Add Column' checkbox to make the 'Planner Value Add' column visible.</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Bias Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_role("treeitem", name="Planner Value Add Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
@@ -899,17 +938,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>F.9</t>
+          <t>F.12</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Check the 'User MAPE Column' checkbox to make the 'User MAPE' column visible.</t>
+          <t>Check the '13W-Fcst Column' checkbox to make the '13W-Fcst' column visible.</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="User MAPE Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_role("treeitem", name="13W-Fcst Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr"/>
@@ -919,17 +958,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>F.10</t>
+          <t>G.1</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Check the 'System MAPE Column' checkbox to make the 'System MAPE' column visible.</t>
+          <t>Click on the column selector element to open the column selection panel.</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System MAPE Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator("div:nth-child(11) &gt; .ag-column-select-column").click()`</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr"/>
@@ -939,17 +978,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>F.11</t>
+          <t>G.2</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Planner Value Add Column' checkbox to make the 'Planner Value Add' column visible.</t>
+          <t>Click on the 'Filter Columns Input' textbox to focus on it for entering a filter value.</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Planner Value Add Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr"/>
@@ -959,17 +998,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>F.12</t>
+          <t>G.3</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Check the '13W-Fcst Column' checkbox to make the '13W-Fcst' column visible.</t>
+          <t>Fill the 'Filter Columns Input' textbox with the value 'Store Count' to filter the columns.</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="13W-Fcst Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("Store Count")`</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
@@ -977,26 +1016,39 @@
       <c r="F28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>--- COLUMN FILTERING ---</t>
-        </is>
-      </c>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>G.4</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Press 'Enter' to apply the filter and display the filtered column options.</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").press("Enter")`</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>G.1</t>
+          <t>G.5</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Click on the column selector element to open the column selection panel.</t>
+          <t>Check the checkbox for the filtered column to make it visible.</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(11) &gt; .ag-column-select-column").click()`</t>
+          <t>`page.get_by_role("checkbox", name="Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr"/>
@@ -1006,17 +1058,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>G.2</t>
+          <t>G.6</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Filter Columns Input' textbox to focus on it for entering a filter value.</t>
+          <t>Click on the 'Columns' button to close the column selection panel.</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
+          <t>`page.get_by_role("button", name="columns").click()`</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr"/>
@@ -1026,17 +1078,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>G.3</t>
+          <t>H.1</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Fill the 'Filter Columns Input' textbox with the value 'Store Count' to filter the columns.</t>
+          <t>Select the radio button for the row with the name '002-SPIRITS' to apply row selection.</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("Store Count")`</t>
+          <t>`page.get_by_role("row", name=" 002-SPIRITS").get_by_role("radio").check()`</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr"/>
@@ -1046,17 +1098,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>G.4</t>
+          <t>H.2</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Press 'Enter' to apply the filter and display the filtered column options.</t>
+          <t>Click on the first 'Filter' button to open the filter configuration for the selected column.</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").press("Enter")`</t>
+          <t>`page.get_by_title("Filter").first.click()`</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr"/>
@@ -1066,17 +1118,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>G.5</t>
+          <t>H.3</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the filtered column to make it visible.</t>
+          <t>Fill the 'Filter Value' textbox with '002-SPIRITS' to filter rows based on this value.</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Value").fill("002-SPIRITS")`</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr"/>
@@ -1086,17 +1138,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>G.6</t>
+          <t>H.4</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Columns' button to close the column selection panel.</t>
+          <t>Click on the 'Apply' button to apply the column filter and update the displayed rows.</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="columns").click()`</t>
+          <t>`page.get_by_label("Column Filter").get_by_role("button", name="Apply").click()`</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr"/>
@@ -1104,26 +1156,39 @@
       <c r="F35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>--- ROW SELECTION AND FILTERING ---</t>
-        </is>
-      </c>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>H.5</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Click on the first 'Filter' button to open the filter configuration for the selected column.</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_title("Filter").first.click()`</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>H.1</t>
+          <t>H.6</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Select the radio button for the row with the name '002-SPIRITS' to apply row selection.</t>
+          <t>Click on the dropdown icon to open the filter condition options.</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("row", name=" 002-SPIRITS").get_by_role("radio").check()`</t>
+          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr"/>
@@ -1133,17 +1198,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>H.2</t>
+          <t>H.7</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Click on the first 'Filter' button to open the filter configuration for the selected column.</t>
+          <t>Select the 'Does not contain' option from the filter condition dropdown.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_title("Filter").first.click()`</t>
+          <t>`page.get_by_role("option", name="Does not contain").click()`</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr"/>
@@ -1153,17 +1218,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>H.3</t>
+          <t>H.8</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Fill the 'Filter Value' textbox with '002-SPIRITS' to filter rows based on this value.</t>
+          <t>Click on the dropdown icon again to open the filter condition options.</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Value").fill("002-SPIRITS")`</t>
+          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr"/>
@@ -1173,17 +1238,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>H.4</t>
+          <t>H.9</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply' button to apply the column filter and update the displayed rows.</t>
+          <t>Select the 'Equals' option from the filter condition dropdown.</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("Column Filter").get_by_role("button", name="Apply").click()`</t>
+          <t>`page.get_by_role("option", name="Equals").click()`</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr"/>
@@ -1193,17 +1258,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>H.5</t>
+          <t>H.10</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Click on the first 'Filter' button to open the filter configuration for the selected column.</t>
+          <t>Click on the dropdown icon again to open the filter condition options.</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_title("Filter").first.click()`</t>
+          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr"/>
@@ -1213,17 +1278,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>H.6</t>
+          <t>H.11</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown icon to open the filter condition options.</t>
+          <t>Select the 'Does not equal' option from the filter condition dropdown.</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
+          <t>`page.get_by_role("option", name="Does not equal").click()`</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr"/>
@@ -1233,17 +1298,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>H.7</t>
+          <t>H.12</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Does not contain' option from the filter condition dropdown.</t>
+          <t>Click on the dropdown icon again to open the filter condition options.</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Does not contain").click()`</t>
+          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr"/>
@@ -1253,17 +1318,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>H.8</t>
+          <t>H.13</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown icon again to open the filter condition options.</t>
+          <t>Select the 'Begins with' option from the filter condition dropdown.</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
+          <t>`page.get_by_role("option", name="Begins with").click()`</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
@@ -1273,17 +1338,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>H.9</t>
+          <t>H.14</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Equals' option from the filter condition dropdown.</t>
+          <t>Click on the dropdown icon again to open the filter condition options.</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Equals").click()`</t>
+          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr"/>
@@ -1293,17 +1358,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>H.10</t>
+          <t>H.15</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown icon again to open the filter condition options.</t>
+          <t>Select the 'Ends with' option from the filter condition dropdown.</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
+          <t>`page.get_by_role("option", name="Ends with").click()`</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr"/>
@@ -1313,17 +1378,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>H.11</t>
+          <t>H.16</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Does not equal' option from the filter condition dropdown.</t>
+          <t>Click on the dropdown icon again to open the filter condition options.</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Does not equal").click()`</t>
+          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
@@ -1333,17 +1398,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>H.12</t>
+          <t>H.17</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown icon again to open the filter condition options.</t>
+          <t>Select the 'Does not contain' option from the filter condition dropdown again.</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
+          <t>`page.get_by_role("option", name="Does not contain").click()`</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr"/>
@@ -1353,17 +1418,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>H.13</t>
+          <t>H.18</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Begins with' option from the filter condition dropdown.</t>
+          <t>Click on the 'Apply' button to apply the selected filter condition.</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Begins with").click()`</t>
+          <t>`page.get_by_label("Column Filter").get_by_role("button", name="Apply").click()`</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr"/>
@@ -1373,17 +1438,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>H.14</t>
+          <t>H.19</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown icon again to open the filter condition options.</t>
+          <t>Click on the first 'Filter' button to reopen the filter configuration.</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
+          <t>`page.get_by_title("Filter").first.click()`</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
@@ -1393,17 +1458,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>H.15</t>
+          <t>H.20</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Ends with' option from the filter condition dropdown.</t>
+          <t>Click on the 'Reset' button to clear the applied filter and reset the filter configuration.</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Ends with").click()`</t>
+          <t>`page.get_by_role("button", name="Reset").click()`</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr"/>
@@ -1413,17 +1478,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>H.16</t>
+          <t>I.1</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown icon again to open the filter condition options.</t>
+          <t>Click on the first pagination link to navigate to the first page of the table.</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
+          <t>`page.locator("a").first.click()`</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr"/>
@@ -1433,17 +1498,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>H.17</t>
+          <t>I.2</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Does not contain' option from the filter condition dropdown again.</t>
+          <t>Click on the second pagination link to navigate to the second page of the table.</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Does not contain").click()`</t>
+          <t>`page.locator("a").nth(1).click()`</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr"/>
@@ -1453,17 +1518,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>H.18</t>
+          <t>I.3</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply' button to apply the selected filter condition.</t>
+          <t>Click on the 'Next' button to navigate to the next page in the pagination.</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("Column Filter").get_by_role("button", name="Apply").click()`</t>
+          <t>`page.locator(".pagination-next &gt; .zeb-chevron-right").first.click()`</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr"/>
@@ -1473,17 +1538,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>H.19</t>
+          <t>I.4</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Click on the first 'Filter' button to reopen the filter configuration.</t>
+          <t>Click on the 'Previous' button to navigate to the previous page in the pagination.</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_title("Filter").first.click()`</t>
+          <t>`page.locator(".zeb-chevron-left").first.click()`</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr"/>
@@ -1493,17 +1558,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>H.20</t>
+          <t>I.5</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Reset' button to clear the applied filter and reset the filter configuration.</t>
+          <t>Click on the 'First' button to navigate to the first page in the pagination.</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Reset").click()`</t>
+          <t>`page.locator(".zeb-nav-to-first").first.click()`</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr"/>
@@ -1511,26 +1576,39 @@
       <c r="F56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>--- PAGINATION INTERACTION ---</t>
-        </is>
-      </c>
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>J.1</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Click on the dropdown to open the row view options.</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".d-flex &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").first.click()`</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>I.1</t>
+          <t>J.2</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Click on the first pagination link to navigate to the first page of the table.</t>
+          <t>Select the option to view 20 rows per page from the dropdown menu.</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("a").first.click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^View 20 row\(s\)$")).first.click()`</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr"/>
@@ -1540,17 +1618,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>I.2</t>
+          <t>J.3</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Click on the second pagination link to navigate to the second page of the table.</t>
+          <t>Click on the dropdown again to open the row view options.</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("a").nth(1).click()`</t>
+          <t>`page.locator(".d-flex &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").first.click()`</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr"/>
@@ -1560,17 +1638,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>I.3</t>
+          <t>J.4</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Next' button to navigate to the next page in the pagination.</t>
+          <t>Select the option to view 50 rows per page from the dropdown menu.</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".pagination-next &gt; .zeb-chevron-right").first.click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^View 50 row\(s\)$")).first.click()`</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr"/>
@@ -1580,17 +1658,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>I.4</t>
+          <t>J.5</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Previous' button to navigate to the previous page in the pagination.</t>
+          <t>Click on the dropdown again to open the row view options.</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".zeb-chevron-left").first.click()`</t>
+          <t>`page.locator(".d-flex &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").first.click()`</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
@@ -1600,17 +1678,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>I.5</t>
+          <t>J.6</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'First' button to navigate to the first page in the pagination.</t>
+          <t>Select the option to view 10 rows per page from the dropdown menu.</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".zeb-nav-to-first").first.click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^View 10 row\(s\)$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr"/>
@@ -1618,26 +1696,39 @@
       <c r="F62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>--- ROW VIEW OPTIONS ---</t>
-        </is>
-      </c>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>J.7</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Click on the text displaying the current row count and total rows to view detailed information.</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Locations 20 rows out of 968").click()`</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>J.1</t>
+          <t>K.1</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown to open the row view options.</t>
+          <t>Click on the right-facing chevron icon to expand the collapsed section.</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").first.click()`</t>
+          <t>`page.locator(".pointer.chevron.zeb-chevron-right.m-r-12.collapsed").click()`</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr"/>
@@ -1647,17 +1738,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>J.2</t>
+          <t>K.2</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Select the option to view 20 rows per page from the dropdown menu.</t>
+          <t>Click on the "Locations" tab to navigate to the Locations section.</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^View 20 row\(s\)$")).first.click()`</t>
+          <t>`page.get_by_text("Locations", exact=True).click()`</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr"/>
@@ -1667,17 +1758,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>J.3</t>
+          <t>K.3</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown again to open the row view options.</t>
+          <t>Uncheck the checkbox in the row labeled "Location" to deselect it.</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").first.click()`</t>
+          <t>`page.get_by_role("row", name="Location").get_by_role("checkbox").uncheck()`</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr"/>
@@ -1687,17 +1778,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>J.4</t>
+          <t>K.4</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Select the option to view 50 rows per page from the dropdown menu.</t>
+          <t>Click on the "Columns" button to open the column visibility options.</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^View 50 row\(s\)$")).first.click()`</t>
+          <t>`page.get_by_role("button", name="columns").nth(1).click()`</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr"/>
@@ -1707,17 +1798,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>J.5</t>
+          <t>K.5</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown again to open the row view options.</t>
+          <t>Uncheck the "Toggle All Columns Visibility" checkbox to hide all columns.</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").first.click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr"/>
@@ -1727,17 +1818,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>J.6</t>
+          <t>K.6</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Select the option to view 10 rows per page from the dropdown menu.</t>
+          <t>Check the "Store Count Column" checkbox to make the Store Count column visible.</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^View 10 row\(s\)$")).nth(1).click()`</t>
+          <t>`page.get_by_role("treeitem", name="Store Count Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr"/>
@@ -1747,17 +1838,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>J.7</t>
+          <t>K.7</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Click on the text displaying the current row count and total rows to view detailed information.</t>
+          <t>Check the "Product Count Column" checkbox to make the Product Count column visible.</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Locations 20 rows out of 968").click()`</t>
+          <t>`page.get_by_role("treeitem", name="Product Count Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr"/>
@@ -1765,26 +1856,39 @@
       <c r="F70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>--- LOCATION AND COLUMN VISIBILITY ---</t>
-        </is>
-      </c>
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>K.8</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Check the "13W-Fcst Column" checkbox to make the 13W-Fcst column visible.</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("treeitem", name="13W-Fcst Column").get_by_label("Press SPACE to toggle").check()`</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>K.1</t>
+          <t>K.9</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Click on the right-facing chevron icon to expand the collapsed section.</t>
+          <t>Click on the "Filter Columns Input" textbox to activate it for typing.</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".pointer.chevron.zeb-chevron-right.m-r-12.collapsed").click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr"/>
@@ -1794,17 +1898,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>K.2</t>
+          <t>K.10</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Locations" tab to navigate to the Locations section.</t>
+          <t>Type "Pre" into the "Filter Columns Input" textbox to filter the column list.</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Locations", exact=True).click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("Pre")`</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr"/>
@@ -1814,17 +1918,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>K.3</t>
+          <t>K.11</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the checkbox in the row labeled "Location" to deselect it.</t>
+          <t>Check the filtered checkbox labeled "Press SPACE to toggle" to make the column visible.</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("row", name="Location").get_by_role("checkbox").uncheck()`</t>
+          <t>`page.get_by_role("checkbox", name="Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr"/>
@@ -1834,12 +1938,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>K.4</t>
+          <t>K.12</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Columns" button to open the column visibility options.</t>
+          <t>Click on the "Columns" button again to close the column visibility options.</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -1854,17 +1958,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>K.5</t>
+          <t>L.1</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the "Toggle All Columns Visibility" checkbox to hide all columns.</t>
+          <t>Click on the filter icon located in the column header to open the column menu.</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
+          <t>`page.locator("#ag-header-cell-menu-button &gt; .filter-icon").click()`</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr"/>
@@ -1874,17 +1978,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>K.6</t>
+          <t>L.2</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Check the "Store Count Column" checkbox to make the Store Count column visible.</t>
+          <t>Click on the "Filter Value" textbox to activate it for typing.</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Store Count Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Value").click()`</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr"/>
@@ -1894,17 +1998,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>K.7</t>
+          <t>L.3</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Check the "Product Count Column" checkbox to make the Product Count column visible.</t>
+          <t>Type "CHICAGO" into the "Filter Value" textbox to filter the rows.</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Product Count Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Value").fill("CHICAGO")`</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr"/>
@@ -1914,17 +2018,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>K.8</t>
+          <t>L.4</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Check the "13W-Fcst Column" checkbox to make the 13W-Fcst column visible.</t>
+          <t>Click on the "Apply" button in the column menu to apply the filter.</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="13W-Fcst Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_label("Column Menu").get_by_role("button", name="Apply").click()`</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr"/>
@@ -1934,17 +2038,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>K.9</t>
+          <t>L.5</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Filter Columns Input" textbox to activate it for typing.</t>
+          <t>Check the checkbox in the grid cell labeled "00162-1554 E 55TH ST-CHICAGO-" to select the row.</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
+          <t>`page.get_by_role("gridcell", name="00162-1554 E 55TH ST-CHICAGO-").get_by_role("checkbox").check()`</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr"/>
@@ -1954,17 +2058,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>K.10</t>
+          <t>L.6</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Type "Pre" into the "Filter Columns Input" textbox to filter the column list.</t>
+          <t>Click on the filter icon in the column header again to reopen the column menu.</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("Pre")`</t>
+          <t>`page.locator("#ag-header-cell-menu-button &gt; .filter-icon").click()`</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr"/>
@@ -1974,17 +2078,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>K.11</t>
+          <t>L.7</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Check the filtered checkbox labeled "Press SPACE to toggle" to make the column visible.</t>
+          <t>Click on the "Reset" button in the column menu to clear the applied filter.</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_label("Column Menu").get_by_role("button", name="Reset").click()`</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr"/>
@@ -1994,17 +2098,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>K.12</t>
+          <t>M.1</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Columns" button again to close the column visibility options.</t>
+          <t>Select the checkbox in the row labeled "Location" to mark it for pagination testing.</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="columns").nth(1).click()`</t>
+          <t>`page.get_by_role("row", name="Location").get_by_role("checkbox").check()`</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr"/>
@@ -2012,26 +2116,39 @@
       <c r="F83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>--- COLUMN MENU FILTERING ---</t>
-        </is>
-      </c>
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>M.2</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Click on the page number "2" link to navigate to the second page of results.</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("a").filter(has_text="2").nth(1).click()`</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr"/>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>L.1</t>
+          <t>M.3</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Click on the filter icon located in the column header to open the column menu.</t>
+          <t>Click on the page number "3" link to navigate to the third page of results.</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#ag-header-cell-menu-button &gt; .filter-icon").click()`</t>
+          <t>`page.locator("a").filter(has_text="3").nth(1).click()`</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr"/>
@@ -2041,17 +2158,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>L.2</t>
+          <t>M.4</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Filter Value" textbox to activate it for typing.</t>
+          <t>Click on the "Next" button (right arrow) to move to the next page of results.</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Value").click()`</t>
+          <t>`page.locator("div:nth-child(3) &gt; esp-pagination-v2 &gt; .d-flex.w-100 &gt; .pagination-pager &gt; .pagination-next &gt; .zeb-chevron-right").click()`</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr"/>
@@ -2061,17 +2178,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>L.3</t>
+          <t>M.5</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Type "CHICAGO" into the "Filter Value" textbox to filter the rows.</t>
+          <t>Click on the "Previous" button (left arrow) to return to the previous page of results.</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Value").fill("CHICAGO")`</t>
+          <t>`page.locator("div:nth-child(3) &gt; esp-pagination-v2 &gt; .d-flex.w-100 &gt; .pagination-pager &gt; .pagination-previous &gt; .zeb-chevron-left").click()`</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr"/>
@@ -2081,17 +2198,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>L.4</t>
+          <t>M.6</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Apply" button in the column menu to apply the filter.</t>
+          <t>Click on the "First" button to navigate back to the first page of results.</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("Column Menu").get_by_role("button", name="Apply").click()`</t>
+          <t>`page.locator("div:nth-child(3) &gt; esp-pagination-v2 &gt; .d-flex.w-100 &gt; .pagination-pager &gt; .pagination-first &gt; .zeb-nav-to-first").click()`</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr"/>
@@ -2101,17 +2218,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>L.5</t>
+          <t>N.1</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox in the grid cell labeled "00162-1554 E 55TH ST-CHICAGO-" to select the row.</t>
+          <t>Click on the 'Filter' button to expand the filter options.</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("gridcell", name="00162-1554 E 55TH ST-CHICAGO-").get_by_role("checkbox").check()`</t>
+          <t>`page.get_by_text("Filter").nth(2).click()`</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr"/>
@@ -2121,17 +2238,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>L.6</t>
+          <t>N.2</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Click on the filter icon in the column header again to reopen the column menu.</t>
+          <t>Click on the dropdown for the 'Time' filter to view available time range options.</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#ag-header-cell-menu-button &gt; .filter-icon").click()`</t>
+          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr"/>
@@ -2141,17 +2258,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>L.7</t>
+          <t>N.3</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Reset" button in the column menu to clear the applied filter.</t>
+          <t>Select the 'Latest 4 Next 4' option from the 'Time' filter dropdown.</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("Column Menu").get_by_role("button", name="Reset").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 4 Next 4$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr"/>
@@ -2159,26 +2276,39 @@
       <c r="F91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>--- PAGINATION NAVIGATION ---</t>
-        </is>
-      </c>
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>N.4</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Click on the dropdown for the 'Time' filter again to change the selection.</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr"/>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>M.1</t>
+          <t>N.5</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Select the checkbox in the row labeled "Location" to mark it for pagination testing.</t>
+          <t>Select the 'Latest 4 Next 13' option from the 'Time' filter dropdown.</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("row", name="Location").get_by_role("checkbox").check()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 4 Next 13$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr"/>
@@ -2188,17 +2318,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>M.2</t>
+          <t>N.6</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Click on the page number "2" link to navigate to the second page of results.</t>
+          <t>Click on the dropdown for the 'Time' filter again to change the selection.</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("a").filter(has_text="2").nth(1).click()`</t>
+          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr"/>
@@ -2208,17 +2338,17 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>M.3</t>
+          <t>N.7</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Click on the page number "3" link to navigate to the third page of results.</t>
+          <t>Select the 'Latest 13 Next 13' option from the 'Time' filter dropdown.</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("a").filter(has_text="3").nth(1).click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 13 Next 13$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr"/>
@@ -2228,17 +2358,17 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>M.4</t>
+          <t>N.8</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Next" button (right arrow) to move to the next page of results.</t>
+          <t>Click on the dropdown for the 'Time' filter again to change the selection.</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; esp-pagination-v2 &gt; .d-flex.w-100 &gt; .pagination-pager &gt; .pagination-next &gt; .zeb-chevron-right").click()`</t>
+          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr"/>
@@ -2248,17 +2378,17 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>M.5</t>
+          <t>N.9</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Previous" button (left arrow) to return to the previous page of results.</t>
+          <t>Select the 'Latest 52 Next 52' option from the 'Time' filter dropdown.</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; esp-pagination-v2 &gt; .d-flex.w-100 &gt; .pagination-pager &gt; .pagination-previous &gt; .zeb-chevron-left").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 52 Next 52$")).first.click()`</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr"/>
@@ -2268,17 +2398,17 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>M.6</t>
+          <t>N.10</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Click on the "First" button to navigate back to the first page of results.</t>
+          <t>Click on the dropdown for the 'Time' filter again to change the selection.</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; esp-pagination-v2 &gt; .d-flex.w-100 &gt; .pagination-pager &gt; .pagination-first &gt; .zeb-nav-to-first").click()`</t>
+          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr"/>
@@ -2286,26 +2416,39 @@
       <c r="F98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>--- TIME FILTER INTERACTION ---</t>
-        </is>
-      </c>
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>N.11</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Select the 'Latest 104 Next 52' option from the 'Time' filter dropdown.</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 104 Next 52$")).nth(1).click()`</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr"/>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>N.1</t>
+          <t>N.12</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Filter' button to expand the filter options.</t>
+          <t>Click on the dropdown for the 'Time' filter again to reset the selection.</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Filter").nth(2).click()`</t>
+          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr"/>
@@ -2315,17 +2458,17 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>N.2</t>
+          <t>N.13</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown for the 'Time' filter to view available time range options.</t>
+          <t>Select the 'Latest 4 Next 4' option from the 'Time' filter dropdown to reset the filter.</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 4 Next 4$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr"/>
@@ -2335,17 +2478,17 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>N.3</t>
+          <t>O.1</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 4 Next 4' option from the 'Time' filter dropdown.</t>
+          <t>Click on the dropdown for the 'Event' filter to view available event options.</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 4 Next 4$")).nth(1).click()`</t>
+          <t>`page.locator("#event-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr"/>
@@ -2355,17 +2498,17 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>N.4</t>
+          <t>O.2</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown for the 'Time' filter again to change the selection.</t>
+          <t>Click on the first element in the list to expand the filter options.</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr"/>
@@ -2375,17 +2518,17 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>N.5</t>
+          <t>O.3</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 4 Next 13' option from the 'Time' filter dropdown.</t>
+          <t>Click on the 'Search' textbox to focus on it.</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 4 Next 13$")).nth(1).click()`</t>
+          <t>`page.get_by_role("textbox", name="Search").click()`</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr"/>
@@ -2395,17 +2538,17 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>N.6</t>
+          <t>O.4</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown for the 'Time' filter again to change the selection.</t>
+          <t>Fill the 'Search' textbox with the value 'TLC'.</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.get_by_role("textbox", name="Search").fill("TLC")`</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr"/>
@@ -2415,17 +2558,17 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>N.7</t>
+          <t>O.5</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 13 Next 13' option from the 'Time' filter dropdown.</t>
+          <t>Click on the close icon to clear the search input.</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 13 Next 13$")).nth(1).click()`</t>
+          <t>`page.locator(".icon.d-flex.pointer.zeb-close").click()`</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr"/>
@@ -2435,17 +2578,17 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>N.8</t>
+          <t>P.1</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown for the 'Time' filter again to change the selection.</t>
+          <t>Click on the dropdown caret for the 'Ad Location' filter to expand the options.</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".not-allowed &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").first.click()`</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr"/>
@@ -2455,17 +2598,17 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>N.9</t>
+          <t>P.2</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 52 Next 52' option from the 'Time' filter dropdown.</t>
+          <t>Click on the dropdown caret for the 'Ad Location' filter again to view the options.</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 52 Next 52$")).first.click()`</t>
+          <t>`page.locator("#ad-location-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr"/>
@@ -2475,17 +2618,17 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>N.10</t>
+          <t>P.3</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown for the 'Time' filter again to change the selection.</t>
+          <t>Click on the first element in the list to expand the filter options.</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr"/>
@@ -2495,17 +2638,17 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>N.11</t>
+          <t>P.4</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 104 Next 52' option from the 'Time' filter dropdown.</t>
+          <t>Click on the first element in the list again to confirm the selection.</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 104 Next 52$")).nth(1).click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr"/>
@@ -2515,17 +2658,17 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>N.12</t>
+          <t>P.5</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown for the 'Time' filter again to reset the selection.</t>
+          <t>Click on the dropdown caret for the 'Ad Location' filter to collapse the options.</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator("#ad-location-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr"/>
@@ -2535,17 +2678,17 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>N.13</t>
+          <t>Q.1</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 4 Next 4' option from the 'Time' filter dropdown to reset the filter.</t>
+          <t>Click on the dropdown caret for the 'Segment' filter to expand the options.</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 4 Next 4$")).nth(1).click()`</t>
+          <t>`page.locator("#segment-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr"/>
@@ -2553,26 +2696,39 @@
       <c r="F112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>--- EVENT FILTER INTERACTION ---</t>
-        </is>
-      </c>
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>Q.2</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Click on the first element in the list to expand the filter options.</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr"/>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>O.1</t>
+          <t>Q.3</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown for the 'Event' filter to view available event options.</t>
+          <t>Click on the first element in the list again to confirm the selection.</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#event-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr"/>
@@ -2582,17 +2738,17 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>O.2</t>
+          <t>Q.4</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list to expand the filter options.</t>
+          <t>Click on the dropdown caret for the 'Segment' filter to collapse the options.</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator("#segment-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr"/>
@@ -2602,17 +2758,17 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>O.3</t>
+          <t>R.1</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Search' textbox to focus on it.</t>
+          <t>Click on the dropdown for the 'Vendor' filter to expand the options.</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Search").click()`</t>
+          <t>`page.locator("#vendor-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100").click()`</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr"/>
@@ -2622,17 +2778,17 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>O.4</t>
+          <t>R.2</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Fill the 'Search' textbox with the value 'TLC'.</t>
+          <t>Click on the first element in the list to expand the filter options.</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Search").fill("TLC")`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr"/>
@@ -2642,17 +2798,17 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>O.5</t>
+          <t>R.3</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Click on the close icon to clear the search input.</t>
+          <t>Click on the first option in the 'Vendor' filter dropdown to select it.</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".icon.d-flex.pointer.zeb-close").click()`</t>
+          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr"/>
@@ -2660,26 +2816,39 @@
       <c r="F118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>--- AD LOCATION FILTER INTERACTION ---</t>
-        </is>
-      </c>
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>R.4</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Click on the second option in the 'Vendor' filter dropdown to select it.</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(2) &gt; .d-flex").click()`</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr"/>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>P.1</t>
+          <t>R.5</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret for the 'Ad Location' filter to expand the options.</t>
+          <t>Click on the first element in the list again to confirm the selection.</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".not-allowed &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").first.click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr"/>
@@ -2689,17 +2858,17 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>P.2</t>
+          <t>R.6</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret for the 'Ad Location' filter again to view the options.</t>
+          <t>Click on the dropdown caret for the 'Vendor' filter again to view the options.</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#ad-location-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator("#vendor-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr"/>
@@ -2709,17 +2878,17 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>P.3</t>
+          <t>R.7</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list to expand the filter options.</t>
+          <t>Click on the 'Apply' button to apply the selected filters.</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator("button").filter(has_text=re.compile(r"^Apply$")).click()`</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr"/>
@@ -2729,17 +2898,17 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>P.4</t>
+          <t>S.1</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list again to confirm the selection.</t>
+          <t>Click on the dropdown caret to expand the column visibility options.</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator(".ellipses &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr"/>
@@ -2749,17 +2918,17 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>P.5</t>
+          <t>S.2</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret for the 'Ad Location' filter to collapse the options.</t>
+          <t>Click on the first element in the list to expand the filter options.</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#ad-location-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr"/>
@@ -2767,26 +2936,39 @@
       <c r="F124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>--- SEGMENT FILTER INTERACTION ---</t>
-        </is>
-      </c>
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>S.3</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>Select the first checkbox to make the corresponding column visible.</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr"/>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>Q.1</t>
+          <t>S.4</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret for the 'Segment' filter to expand the options.</t>
+          <t>Select the second checkbox to make the corresponding column visible.</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#segment-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr"/>
@@ -2796,17 +2978,17 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>Q.2</t>
+          <t>S.5</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list to expand the filter options.</t>
+          <t>Select the third checkbox to make the corresponding column visible.</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr"/>
@@ -2816,17 +2998,17 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>Q.3</t>
+          <t>S.6</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list again to confirm the selection.</t>
+          <t>Select the fourth checkbox to make the corresponding column visible.</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr"/>
@@ -2836,17 +3018,17 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>Q.4</t>
+          <t>S.7</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret for the 'Segment' filter to collapse the options.</t>
+          <t>Click on the first element in the list again to confirm the selection.</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#segment-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr"/>
@@ -2854,26 +3036,39 @@
       <c r="F129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>--- VENDOR FILTER INTERACTION ---</t>
-        </is>
-      </c>
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>S.8</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>Deselect the first checkbox to hide the corresponding column.</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.deselected").first.click()`</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr"/>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>R.1</t>
+          <t>S.9</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown for the 'Vendor' filter to expand the options.</t>
+          <t>Deselect the second checkbox to hide the corresponding column.</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#vendor-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100").click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.deselected").first.click()`</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr"/>
@@ -2883,17 +3078,17 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>R.2</t>
+          <t>S.10</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list to expand the filter options.</t>
+          <t>Deselect the third checkbox to hide the corresponding column.</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.deselected").first.click()`</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr"/>
@@ -2903,17 +3098,17 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>R.3</t>
+          <t>S.11</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Click on the first option in the 'Vendor' filter dropdown to select it.</t>
+          <t>Click on the fifth element in the list to select a specific column.</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(5)").click()`</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr"/>
@@ -2923,17 +3118,17 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>R.4</t>
+          <t>S.12</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Click on the second option in the 'Vendor' filter dropdown to select it.</t>
+          <t>Click on the dropdown caret again to collapse the column visibility options.</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(2) &gt; .d-flex").click()`</t>
+          <t>`page.locator(".ellipses &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr"/>
@@ -2943,17 +3138,17 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>R.5</t>
+          <t>S.13</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list again to confirm the selection.</t>
+          <t>Click on the dropdown caret for another section to expand its options.</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr"/>
@@ -2963,17 +3158,17 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>R.6</t>
+          <t>S.14</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret for the 'Vendor' filter again to view the options.</t>
+          <t>Click on the first element in the list to expand the filter options.</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#vendor-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr"/>
@@ -2983,17 +3178,17 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>R.7</t>
+          <t>S.15</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply' button to apply the selected filters.</t>
+          <t>Click on the first element in the list again to confirm the selection.</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("button").filter(has_text=re.compile(r"^Apply$")).click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr"/>
@@ -3001,26 +3196,39 @@
       <c r="F137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>--- COLUMN VISIBILITY OPTIONS ---</t>
-        </is>
-      </c>
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>S.16</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>Click on the dropdown caret for another section again to collapse its options.</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr"/>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>S.1</t>
+          <t>S.17</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret to expand the column visibility options.</t>
+          <t>Click on the 'Columns' button to open the column visibility settings.</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ellipses &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.get_by_role("button", name="columns").nth(2).click()`</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr"/>
@@ -3030,17 +3238,17 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>S.2</t>
+          <t>S.18</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list to expand the filter options.</t>
+          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to deselect all columns.</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr"/>
@@ -3050,17 +3258,17 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>S.3</t>
+          <t>S.19</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Select the first checkbox to make the corresponding column visible.</t>
+          <t>Click on the first column in the list to make it visible.</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
+          <t>`page.locator("#ag-6720 &gt; .ag-column-panel &gt; .ag-column-select &gt; .ag-column-select-list &gt; .ag-virtual-list-viewport &gt; .ag-virtual-list-container &gt; div &gt; .ag-column-select-column").first.click()`</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr"/>
@@ -3070,17 +3278,17 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>S.4</t>
+          <t>S.20</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Select the second checkbox to make the corresponding column visible.</t>
+          <t>Check the checkbox for the '/11/2026 Column' to make it visible.</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
+          <t>`page.get_by_role("treeitem", name="/11/2026 Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr"/>
@@ -3090,17 +3298,17 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>S.5</t>
+          <t>S.21</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Select the third checkbox to make the corresponding column visible.</t>
+          <t>Check the checkbox for the '/18/2026 Column' to make it visible.</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
+          <t>`page.get_by_role("treeitem", name="/18/2026 Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr"/>
@@ -3110,17 +3318,17 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>S.6</t>
+          <t>S.22</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Select the fourth checkbox to make the corresponding column visible.</t>
+          <t>Check the checkbox for the '/25/2026 Column' to make it visible.</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
+          <t>`page.get_by_role("treeitem", name="/25/2026 Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr"/>
@@ -3130,17 +3338,17 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>S.7</t>
+          <t>S.23</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list again to confirm the selection.</t>
+          <t>Check the checkbox for the '02/01/2026 Column' to make it visible.</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.get_by_role("treeitem", name="02/01/2026 Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr"/>
@@ -3150,17 +3358,17 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>S.8</t>
+          <t>S.24</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Deselect the first checkbox to hide the corresponding column.</t>
+          <t>Check the checkbox for the '/08/2026 Column' to make it visible.</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.deselected").first.click()`</t>
+          <t>`page.get_by_role("treeitem", name="/08/2026 Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr"/>
@@ -3170,17 +3378,17 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>S.9</t>
+          <t>S.25</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Deselect the second checkbox to hide the corresponding column.</t>
+          <t>Check the 'Toggle All Columns Visibility' checkbox to select all columns.</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.deselected").first.click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr"/>
@@ -3190,17 +3398,17 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>S.10</t>
+          <t>S.26</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Deselect the third checkbox to hide the corresponding column.</t>
+          <t>Click on the 'Columns' button again to close the column visibility settings.</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.deselected").first.click()`</t>
+          <t>`page.get_by_role("button", name="columns").nth(2).click()`</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr"/>
@@ -3210,17 +3418,17 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>S.11</t>
+          <t>T.1</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Click on the fifth element in the list to select a specific column.</t>
+          <t>Click on the dropdown caret to expand the additional column visibility options.</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(5)").click()`</t>
+          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr"/>
@@ -3230,17 +3438,17 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>S.12</t>
+          <t>T.2</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret again to collapse the column visibility options.</t>
+          <t>Click on the first element in the list to expand the filter options.</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ellipses &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr"/>
@@ -3250,17 +3458,17 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>S.13</t>
+          <t>T.3</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret for another section to expand its options.</t>
+          <t>Click on the first element in the list again to confirm the selection.</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr"/>
@@ -3270,17 +3478,17 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>S.14</t>
+          <t>T.4</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list to expand the filter options.</t>
+          <t>Click on the first dropdown option to select it.</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr"/>
@@ -3290,17 +3498,17 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>S.15</t>
+          <t>T.5</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list again to confirm the selection.</t>
+          <t>Click on the first dropdown option again to confirm the selection.</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr"/>
@@ -3310,17 +3518,17 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>S.16</t>
+          <t>T.6</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret for another section again to collapse its options.</t>
+          <t>Click on the first dropdown option once more to finalize the selection.</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr"/>
@@ -3330,17 +3538,17 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>S.17</t>
+          <t>T.7</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Columns' button to open the column visibility settings.</t>
+          <t>Click on the fourth element in the list to select a specific column.</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="columns").nth(2).click()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(4) &gt; .d-flex").click()`</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr"/>
@@ -3350,17 +3558,17 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>S.18</t>
+          <t>T.8</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to deselect all columns.</t>
+          <t>Click on the fifth element in the list to select another specific column.</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
+          <t>`page.locator("div:nth-child(5) &gt; .d-flex").click()`</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr"/>
@@ -3370,17 +3578,17 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>S.19</t>
+          <t>T.9</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Click on the first column in the list to make it visible.</t>
+          <t>Click on the "Maximum User Forecast" option to select it.</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#ag-6720 &gt; .ag-column-panel &gt; .ag-column-select &gt; .ag-column-select-list &gt; .ag-virtual-list-viewport &gt; .ag-virtual-list-container &gt; div &gt; .ag-column-select-column").first.click()`</t>
+          <t>`page.get_by_text("Maximum User Forecast").nth(1).click()`</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr"/>
@@ -3390,17 +3598,17 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>S.20</t>
+          <t>T.10</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the '/11/2026 Column' to make it visible.</t>
+          <t>Click on the "Average User Forecast" option to select it.</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="/11/2026 Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_text("Average User Forecast").nth(1).click()`</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr"/>
@@ -3410,17 +3618,17 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>S.21</t>
+          <t>T.11</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the '/18/2026 Column' to make it visible.</t>
+          <t>Click on the eighth element in the list to select another specific column.</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="/18/2026 Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(8)").click()`</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr"/>
@@ -3430,17 +3638,17 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>S.22</t>
+          <t>T.12</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the '/25/2026 Column' to make it visible.</t>
+          <t>Click on the first dropdown option to finalize the selection.</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="/25/2026 Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.locator(".d-flex.dropdown-option").first.click()`</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr"/>
@@ -3450,17 +3658,17 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>S.23</t>
+          <t>T.13</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the '02/01/2026 Column' to make it visible.</t>
+          <t>Click on the dropdown caret again to collapse the additional column visibility options.</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="02/01/2026 Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr"/>
@@ -3470,17 +3678,17 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>S.24</t>
+          <t>T.14</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the '/08/2026 Column' to make it visible.</t>
+          <t>Click on the third element in the list to select a specific column.</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="/08/2026 Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator("div:nth-child(3) &gt; span &gt; .align-middle").click()`</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr"/>
@@ -3490,17 +3698,17 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>S.25</t>
+          <t>T.15</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Toggle All Columns Visibility' checkbox to select all columns.</t>
+          <t>Click on the filter icon in the header to open the filter settings.</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
+          <t>`page.locator(".ag-header-cell.ag-header-parent-hidden.ag-header-cell-sortable.ag-header-background.ag-focus-managed.ag-header-active &gt; .ag-header-cell-comp-wrapper &gt; .ag-cell-label-container &gt; .ag-header-icon &gt; .filter-icon").click()`</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr"/>
@@ -3510,17 +3718,17 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>S.26</t>
+          <t>T.16</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Columns' button again to close the column visibility settings.</t>
+          <t>Click on the "Apply" button in the filter settings to apply the changes.</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="columns").nth(2).click()`</t>
+          <t>`page.get_by_label("Column Filter").get_by_role("button", name="Apply").click()`</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr"/>
@@ -3528,26 +3736,39 @@
       <c r="F164" s="4" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>--- ADDITIONAL COLUMN VISIBILITY SETTINGS ---</t>
-        </is>
-      </c>
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>T.17</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Columns' button to open the column visibility settings.</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("button", name="columns").nth(3).click()`</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr"/>
+      <c r="E165" s="4" t="inlineStr"/>
+      <c r="F165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>T.1</t>
+          <t>T.18</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret to expand the additional column visibility options.</t>
+          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to deselect all columns.</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr"/>
@@ -3557,17 +3778,17 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>T.2</t>
+          <t>T.19</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list to expand the filter options.</t>
+          <t>Check the checkbox for the 'Start Week Column' to make it visible.</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.get_by_role("treeitem", name="Start Week Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr"/>
@@ -3577,17 +3798,17 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>T.3</t>
+          <t>T.20</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list again to confirm the selection.</t>
+          <t>Check the checkbox for the 'End Week Column' to make it visible.</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.get_by_role("treeitem", name="End Week Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr"/>
@@ -3597,17 +3818,17 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>T.4</t>
+          <t>T.21</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Click on the first dropdown option to select it.</t>
+          <t>Check the checkbox for the 'Clone Column' to make it visible.</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
+          <t>`page.get_by_role("treeitem", name="Clone Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr"/>
@@ -3617,17 +3838,17 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>T.5</t>
+          <t>T.22</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Click on the first dropdown option again to confirm the selection.</t>
+          <t>Check the checkbox for the 'Event Column' to make it visible.</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
+          <t>`page.get_by_role("treeitem", name="Event Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr"/>
@@ -3637,17 +3858,17 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>T.6</t>
+          <t>T.23</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Click on the first dropdown option once more to finalize the selection.</t>
+          <t>Check the checkbox for the 'Market Column' to make it visible.</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
+          <t>`page.get_by_role("treeitem", name="Market Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr"/>
@@ -3657,17 +3878,17 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>T.7</t>
+          <t>T.24</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Click on the fourth element in the list to select a specific column.</t>
+          <t>Check the checkbox for the 'Count of Stores Column' to make it visible.</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(4) &gt; .d-flex").click()`</t>
+          <t>`page.get_by_role("treeitem", name="Count of Stores Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr"/>
@@ -3677,17 +3898,17 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>T.8</t>
+          <t>T.25</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Click on the fifth element in the list to select another specific column.</t>
+          <t>Check the checkbox for the 'Spot Column' to make it visible.</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(5) &gt; .d-flex").click()`</t>
+          <t>`page.get_by_role("treeitem", name="Spot Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr"/>
@@ -3697,17 +3918,17 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>T.9</t>
+          <t>T.26</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Maximum User Forecast" option to select it.</t>
+          <t>Check the 'Toggle All Columns Visibility' checkbox to select all columns.</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Maximum User Forecast").nth(1).click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr"/>
@@ -3717,17 +3938,17 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>T.10</t>
+          <t>T.27</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Average User Forecast" option to select it.</t>
+          <t>Click on the 'Columns' button again to close the column visibility settings.</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Average User Forecast").nth(1).click()`</t>
+          <t>`page.get_by_role("button", name="columns").nth(3).click()`</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr"/>
@@ -3737,17 +3958,17 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>T.11</t>
+          <t>U.1</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Click on the eighth element in the list to select another specific column.</t>
+          <t>Click on the page number "2" link to navigate to the second page of the results.</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(8)").click()`</t>
+          <t>`page.locator("a").filter(has_text="2").nth(2).click()`</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr"/>
@@ -3757,17 +3978,17 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>T.12</t>
+          <t>U.2</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Click on the first dropdown option to finalize the selection.</t>
+          <t>Click on the page number "3" link to navigate to the third page of the results.</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.dropdown-option").first.click()`</t>
+          <t>`page.locator("a").filter(has_text="3").nth(2).click()`</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr"/>
@@ -3777,391 +3998,26 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>T.13</t>
+          <t>U.3</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret again to collapse the additional column visibility options.</t>
+          <t>Click on the "First Page" button in the pagination controls to navigate back to the first page of the results.</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator("div:nth-child(7) &gt; div &gt; .componentParentWrapper &gt; esp-grid-container &gt; esp-card-component &gt; .card-container &gt; .card-content &gt; esp-row-dimentional-grid &gt; div &gt; #paginationId &gt; esp-pagination-v2 &gt; .d-flex.w-100 &gt; .pagination-pager &gt; .pagination-first").click()`</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr"/>
       <c r="E178" s="4" t="inlineStr"/>
       <c r="F178" s="4" t="inlineStr"/>
     </row>
-    <row r="179">
-      <c r="A179" s="3" t="inlineStr">
-        <is>
-          <t>T.14</t>
-        </is>
-      </c>
-      <c r="B179" s="4" t="inlineStr">
-        <is>
-          <t>Click on the third element in the list to select a specific column.</t>
-        </is>
-      </c>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("div:nth-child(3) &gt; span &gt; .align-middle").click()`</t>
-        </is>
-      </c>
-      <c r="D179" s="3" t="inlineStr"/>
-      <c r="E179" s="4" t="inlineStr"/>
-      <c r="F179" s="4" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="3" t="inlineStr">
-        <is>
-          <t>T.15</t>
-        </is>
-      </c>
-      <c r="B180" s="4" t="inlineStr">
-        <is>
-          <t>Click on the filter icon in the header to open the filter settings.</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".ag-header-cell.ag-header-parent-hidden.ag-header-cell-sortable.ag-header-background.ag-focus-managed.ag-header-active &gt; .ag-header-cell-comp-wrapper &gt; .ag-cell-label-container &gt; .ag-header-icon &gt; .filter-icon").click()`</t>
-        </is>
-      </c>
-      <c r="D180" s="3" t="inlineStr"/>
-      <c r="E180" s="4" t="inlineStr"/>
-      <c r="F180" s="4" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="3" t="inlineStr">
-        <is>
-          <t>T.16</t>
-        </is>
-      </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>Click on the "Apply" button in the filter settings to apply the changes.</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_label("Column Filter").get_by_role("button", name="Apply").click()`</t>
-        </is>
-      </c>
-      <c r="D181" s="3" t="inlineStr"/>
-      <c r="E181" s="4" t="inlineStr"/>
-      <c r="F181" s="4" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="3" t="inlineStr">
-        <is>
-          <t>T.17</t>
-        </is>
-      </c>
-      <c r="B182" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'Columns' button to open the column visibility settings.</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("button", name="columns").nth(3).click()`</t>
-        </is>
-      </c>
-      <c r="D182" s="3" t="inlineStr"/>
-      <c r="E182" s="4" t="inlineStr"/>
-      <c r="F182" s="4" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="3" t="inlineStr">
-        <is>
-          <t>T.18</t>
-        </is>
-      </c>
-      <c r="B183" s="4" t="inlineStr">
-        <is>
-          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to deselect all columns.</t>
-        </is>
-      </c>
-      <c r="C183" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="inlineStr"/>
-      <c r="E183" s="4" t="inlineStr"/>
-      <c r="F183" s="4" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="3" t="inlineStr">
-        <is>
-          <t>T.19</t>
-        </is>
-      </c>
-      <c r="B184" s="4" t="inlineStr">
-        <is>
-          <t>Check the checkbox for the 'Start Week Column' to make it visible.</t>
-        </is>
-      </c>
-      <c r="C184" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("treeitem", name="Start Week Column").get_by_label("Press SPACE to toggle").check()`</t>
-        </is>
-      </c>
-      <c r="D184" s="3" t="inlineStr"/>
-      <c r="E184" s="4" t="inlineStr"/>
-      <c r="F184" s="4" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="3" t="inlineStr">
-        <is>
-          <t>T.20</t>
-        </is>
-      </c>
-      <c r="B185" s="4" t="inlineStr">
-        <is>
-          <t>Check the checkbox for the 'End Week Column' to make it visible.</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("treeitem", name="End Week Column").get_by_label("Press SPACE to toggle").check()`</t>
-        </is>
-      </c>
-      <c r="D185" s="3" t="inlineStr"/>
-      <c r="E185" s="4" t="inlineStr"/>
-      <c r="F185" s="4" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="3" t="inlineStr">
-        <is>
-          <t>T.21</t>
-        </is>
-      </c>
-      <c r="B186" s="4" t="inlineStr">
-        <is>
-          <t>Check the checkbox for the 'Clone Column' to make it visible.</t>
-        </is>
-      </c>
-      <c r="C186" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("treeitem", name="Clone Column").get_by_label("Press SPACE to toggle").check()`</t>
-        </is>
-      </c>
-      <c r="D186" s="3" t="inlineStr"/>
-      <c r="E186" s="4" t="inlineStr"/>
-      <c r="F186" s="4" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="3" t="inlineStr">
-        <is>
-          <t>T.22</t>
-        </is>
-      </c>
-      <c r="B187" s="4" t="inlineStr">
-        <is>
-          <t>Check the checkbox for the 'Event Column' to make it visible.</t>
-        </is>
-      </c>
-      <c r="C187" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("treeitem", name="Event Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
-        </is>
-      </c>
-      <c r="D187" s="3" t="inlineStr"/>
-      <c r="E187" s="4" t="inlineStr"/>
-      <c r="F187" s="4" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="3" t="inlineStr">
-        <is>
-          <t>T.23</t>
-        </is>
-      </c>
-      <c r="B188" s="4" t="inlineStr">
-        <is>
-          <t>Check the checkbox for the 'Market Column' to make it visible.</t>
-        </is>
-      </c>
-      <c r="C188" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("treeitem", name="Market Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
-        </is>
-      </c>
-      <c r="D188" s="3" t="inlineStr"/>
-      <c r="E188" s="4" t="inlineStr"/>
-      <c r="F188" s="4" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="3" t="inlineStr">
-        <is>
-          <t>T.24</t>
-        </is>
-      </c>
-      <c r="B189" s="4" t="inlineStr">
-        <is>
-          <t>Check the checkbox for the 'Count of Stores Column' to make it visible.</t>
-        </is>
-      </c>
-      <c r="C189" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("treeitem", name="Count of Stores Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
-        </is>
-      </c>
-      <c r="D189" s="3" t="inlineStr"/>
-      <c r="E189" s="4" t="inlineStr"/>
-      <c r="F189" s="4" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="3" t="inlineStr">
-        <is>
-          <t>T.25</t>
-        </is>
-      </c>
-      <c r="B190" s="4" t="inlineStr">
-        <is>
-          <t>Check the checkbox for the 'Spot Column' to make it visible.</t>
-        </is>
-      </c>
-      <c r="C190" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("treeitem", name="Spot Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
-        </is>
-      </c>
-      <c r="D190" s="3" t="inlineStr"/>
-      <c r="E190" s="4" t="inlineStr"/>
-      <c r="F190" s="4" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="3" t="inlineStr">
-        <is>
-          <t>T.26</t>
-        </is>
-      </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
-          <t>Check the 'Toggle All Columns Visibility' checkbox to select all columns.</t>
-        </is>
-      </c>
-      <c r="C191" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
-        </is>
-      </c>
-      <c r="D191" s="3" t="inlineStr"/>
-      <c r="E191" s="4" t="inlineStr"/>
-      <c r="F191" s="4" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="3" t="inlineStr">
-        <is>
-          <t>T.27</t>
-        </is>
-      </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'Columns' button again to close the column visibility settings.</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("button", name="columns").nth(3).click()`</t>
-        </is>
-      </c>
-      <c r="D192" s="3" t="inlineStr"/>
-      <c r="E192" s="4" t="inlineStr"/>
-      <c r="F192" s="4" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>--- FINAL PAGINATION NAVIGATION ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="3" t="inlineStr">
-        <is>
-          <t>U.1</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>Click on the page number "2" link to navigate to the second page of the results.</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("a").filter(has_text="2").nth(2).click()`</t>
-        </is>
-      </c>
-      <c r="D194" s="3" t="inlineStr"/>
-      <c r="E194" s="4" t="inlineStr"/>
-      <c r="F194" s="4" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="3" t="inlineStr">
-        <is>
-          <t>U.2</t>
-        </is>
-      </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>Click on the page number "3" link to navigate to the third page of the results.</t>
-        </is>
-      </c>
-      <c r="C195" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("a").filter(has_text="3").nth(2).click()`</t>
-        </is>
-      </c>
-      <c r="D195" s="3" t="inlineStr"/>
-      <c r="E195" s="4" t="inlineStr"/>
-      <c r="F195" s="4" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="3" t="inlineStr">
-        <is>
-          <t>U.3</t>
-        </is>
-      </c>
-      <c r="B196" s="4" t="inlineStr">
-        <is>
-          <t>Click on the "First Page" button in the pagination controls to navigate back to the first page of the results.</t>
-        </is>
-      </c>
-      <c r="C196" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("div:nth-child(7) &gt; div &gt; .componentParentWrapper &gt; esp-grid-container &gt; esp-card-component &gt; .card-container &gt; .card-content &gt; esp-row-dimentional-grid &gt; div &gt; #paginationId &gt; esp-pagination-v2 &gt; .d-flex.w-100 &gt; .pagination-pager &gt; .pagination-first").click()`</t>
-        </is>
-      </c>
-      <c r="D196" s="3" t="inlineStr"/>
-      <c r="E196" s="4" t="inlineStr"/>
-      <c r="F196" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A99:F99"/>
-    <mergeCell ref="A84:F84"/>
-    <mergeCell ref="A193:F193"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
+  <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A165:F165"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A125:F125"/>
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="A92:F92"/>
-    <mergeCell ref="A130:F130"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A138:F138"/>
-    <mergeCell ref="A119:F119"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/UAT_Excel_Reports/Wba Alerts_UAT.xlsx
+++ b/UAT_Excel_Reports/Wba Alerts_UAT.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F178"/>
+  <dimension ref="A1:F196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -496,39 +496,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>D.1</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Open the Executive Dashboard page by navigating to the specified URL.</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>`page.goto("https://stage.wba.esp.antuit.ai/dp/demand-planning/executive-dashboard?workbookId=6&amp;tabIndex=1")`</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>--- NAVIGATION TO DASHBOARD ---</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>E.1</t>
+          <t>D.1</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Alerts' filter dropdown to expand the filter options.</t>
+          <t>Open the Executive Dashboard page by navigating to the specified URL.</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#alerts-filterId").click()`</t>
+          <t>`page.goto("https://stage.wba.esp.antuit.ai/dp/demand-planning/executive-dashboard?workbookId=6&amp;tabIndex=1")`</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
@@ -536,39 +523,26 @@
       <c r="F4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>E.2</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>From the dropdown list, select the 'MAPE' option to apply the filter.</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^MAPE$")).nth(1).click()`</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>--- ALERTS FILTER INTERACTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>E.3</t>
+          <t>E.1</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret to open the filter options again.</t>
+          <t>Click on the 'Alerts' filter dropdown to expand the filter options.</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator("#alerts-filterId").click()`</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
@@ -578,17 +552,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>E.4</t>
+          <t>E.2</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>From the dropdown list, select the 'Under Bias' option to apply the filter.</t>
+          <t>From the dropdown list, select the 'MAPE' option to apply the filter.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Under Bias$")).nth(1).click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^MAPE$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
@@ -598,7 +572,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>E.5</t>
+          <t>E.3</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -618,17 +592,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>E.6</t>
+          <t>E.4</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>From the dropdown list, select the 'Over Bias' option to apply the filter.</t>
+          <t>From the dropdown list, select the 'Under Bias' option to apply the filter.</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Over Bias$")).nth(1).click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Under Bias$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
@@ -638,7 +612,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>E.7</t>
+          <t>E.5</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -658,17 +632,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>E.8</t>
+          <t>E.6</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>From the dropdown list, select the 'PVA' option to apply the filter.</t>
+          <t>From the dropdown list, select the 'Over Bias' option to apply the filter.</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^PVA$")).nth(1).click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Over Bias$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr"/>
@@ -678,7 +652,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>E.9</t>
+          <t>E.7</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -698,17 +672,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>E.10</t>
+          <t>E.8</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>From the dropdown list, select the 'SSIS' option to apply the filter.</t>
+          <t>From the dropdown list, select the 'PVA' option to apply the filter.</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^SSIS$")).first.click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^PVA$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -718,17 +692,17 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>F.1</t>
+          <t>E.9</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Columns' button to open the column visibility configuration panel.</t>
+          <t>Click on the dropdown caret to open the filter options again.</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="columns").click()`</t>
+          <t>`page.locator(".w-100.p-h-16.p-v-8.dropdown-label.background-white &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr"/>
@@ -738,17 +712,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>F.2</t>
+          <t>E.10</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to hide all columns initially.</t>
+          <t>From the dropdown list, select the 'SSIS' option to apply the filter.</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^SSIS$")).first.click()`</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr"/>
@@ -756,39 +730,26 @@
       <c r="F15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>F.3</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Check the 'Store Count Column' checkbox to make the 'Store Count' column visible.</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("treeitem", name="Store Count Column").get_by_label("Press SPACE to toggle").check()`</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>--- COLUMN VISIBILITY CONFIGURATION ---</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>F.4</t>
+          <t>F.1</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Product Count Column' checkbox to make the 'Product Count' column visible.</t>
+          <t>Click on the 'Columns' button to open the column visibility configuration panel.</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Product Count Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_role("button", name="columns").click()`</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr"/>
@@ -798,17 +759,17 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>F.5</t>
+          <t>F.2</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Stability Column' checkbox to make the 'Stability' column visible.</t>
+          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to hide all columns initially.</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Stability Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr"/>
@@ -818,17 +779,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>F.6</t>
+          <t>F.3</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Check the 'SSIS Column' checkbox to make the 'SSIS' column visible.</t>
+          <t>Check the 'Store Count Column' checkbox to make the 'Store Count' column visible.</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="SSIS Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_role("treeitem", name="Store Count Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr"/>
@@ -838,17 +799,17 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>F.7</t>
+          <t>F.4</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Check the 'User Bias Column' checkbox to make the 'User Bias' column visible.</t>
+          <t>Check the 'Product Count Column' checkbox to make the 'Product Count' column visible.</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="User Bias Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_role("treeitem", name="Product Count Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr"/>
@@ -858,17 +819,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>F.8</t>
+          <t>F.5</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Check the 'System Bias Column' checkbox to make the 'System Bias' column visible.</t>
+          <t>Check the 'Stability Column' checkbox to make the 'Stability' column visible.</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System Bias Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_role("treeitem", name="Stability Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
@@ -878,17 +839,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>F.9</t>
+          <t>F.6</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Check the 'User MAPE Column' checkbox to make the 'User MAPE' column visible.</t>
+          <t>Check the 'SSIS Column' checkbox to make the 'SSIS' column visible.</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="User MAPE Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_role("treeitem", name="SSIS Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
@@ -898,17 +859,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>F.10</t>
+          <t>F.7</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Check the 'System MAPE Column' checkbox to make the 'System MAPE' column visible.</t>
+          <t>Check the 'User Bias Column' checkbox to make the 'User Bias' column visible.</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="System MAPE Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_role("treeitem", name="User Bias Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr"/>
@@ -918,17 +879,17 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>F.11</t>
+          <t>F.8</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Planner Value Add Column' checkbox to make the 'Planner Value Add' column visible.</t>
+          <t>Check the 'System Bias Column' checkbox to make the 'System Bias' column visible.</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Planner Value Add Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_role("treeitem", name="System Bias Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
@@ -938,17 +899,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>F.12</t>
+          <t>F.9</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Check the '13W-Fcst Column' checkbox to make the '13W-Fcst' column visible.</t>
+          <t>Check the 'User MAPE Column' checkbox to make the 'User MAPE' column visible.</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="13W-Fcst Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.get_by_role("treeitem", name="User MAPE Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr"/>
@@ -958,17 +919,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>G.1</t>
+          <t>F.10</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Click on the column selector element to open the column selection panel.</t>
+          <t>Check the 'System MAPE Column' checkbox to make the 'System MAPE' column visible.</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(11) &gt; .ag-column-select-column").click()`</t>
+          <t>`page.get_by_role("treeitem", name="System MAPE Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr"/>
@@ -978,17 +939,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>G.2</t>
+          <t>F.11</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Filter Columns Input' textbox to focus on it for entering a filter value.</t>
+          <t>Check the 'Planner Value Add Column' checkbox to make the 'Planner Value Add' column visible.</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
+          <t>`page.get_by_role("treeitem", name="Planner Value Add Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr"/>
@@ -998,17 +959,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>G.3</t>
+          <t>F.12</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Fill the 'Filter Columns Input' textbox with the value 'Store Count' to filter the columns.</t>
+          <t>Check the '13W-Fcst Column' checkbox to make the '13W-Fcst' column visible.</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("Store Count")`</t>
+          <t>`page.get_by_role("treeitem", name="13W-Fcst Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
@@ -1016,39 +977,26 @@
       <c r="F28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>G.4</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Press 'Enter' to apply the filter and display the filtered column options.</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").press("Enter")`</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>--- COLUMN FILTERING ---</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>G.5</t>
+          <t>G.1</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the filtered column to make it visible.</t>
+          <t>Click on the column selector element to open the column selection panel.</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Press SPACE to toggle").check()`</t>
+          <t>`page.locator("div:nth-child(11) &gt; .ag-column-select-column").click()`</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr"/>
@@ -1058,17 +1006,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>G.6</t>
+          <t>G.2</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Columns' button to close the column selection panel.</t>
+          <t>Click on the 'Filter Columns Input' textbox to focus on it for entering a filter value.</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="columns").click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr"/>
@@ -1078,17 +1026,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>H.1</t>
+          <t>G.3</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Select the radio button for the row with the name '002-SPIRITS' to apply row selection.</t>
+          <t>Fill the 'Filter Columns Input' textbox with the value 'Store Count' to filter the columns.</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("row", name=" 002-SPIRITS").get_by_role("radio").check()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("Store Count")`</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr"/>
@@ -1098,17 +1046,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>H.2</t>
+          <t>G.4</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Click on the first 'Filter' button to open the filter configuration for the selected column.</t>
+          <t>Press 'Enter' to apply the filter and display the filtered column options.</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_title("Filter").first.click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").press("Enter")`</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr"/>
@@ -1118,17 +1066,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>H.3</t>
+          <t>G.5</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Fill the 'Filter Value' textbox with '002-SPIRITS' to filter rows based on this value.</t>
+          <t>Check the checkbox for the filtered column to make it visible.</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Value").fill("002-SPIRITS")`</t>
+          <t>`page.get_by_role("checkbox", name="Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr"/>
@@ -1138,17 +1086,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>H.4</t>
+          <t>G.6</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply' button to apply the column filter and update the displayed rows.</t>
+          <t>Click on the 'Columns' button to close the column selection panel.</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("Column Filter").get_by_role("button", name="Apply").click()`</t>
+          <t>`page.get_by_role("button", name="columns").click()`</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr"/>
@@ -1156,39 +1104,26 @@
       <c r="F35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>H.5</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Click on the first 'Filter' button to open the filter configuration for the selected column.</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_title("Filter").first.click()`</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>--- ROW SELECTION AND FILTERING ---</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>H.6</t>
+          <t>H.1</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown icon to open the filter condition options.</t>
+          <t>Select the radio button for the row with the name '002-SPIRITS' to apply row selection.</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
+          <t>`page.get_by_role("row", name=" 002-SPIRITS").get_by_role("radio").check()`</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr"/>
@@ -1198,17 +1133,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>H.7</t>
+          <t>H.2</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Does not contain' option from the filter condition dropdown.</t>
+          <t>Click on the first 'Filter' button to open the filter configuration for the selected column.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Does not contain").click()`</t>
+          <t>`page.get_by_title("Filter").first.click()`</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr"/>
@@ -1218,17 +1153,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>H.8</t>
+          <t>H.3</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown icon again to open the filter condition options.</t>
+          <t>Fill the 'Filter Value' textbox with '002-SPIRITS' to filter rows based on this value.</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Value").fill("002-SPIRITS")`</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr"/>
@@ -1238,17 +1173,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>H.9</t>
+          <t>H.4</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Equals' option from the filter condition dropdown.</t>
+          <t>Click on the 'Apply' button to apply the column filter and update the displayed rows.</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Equals").click()`</t>
+          <t>`page.get_by_label("Column Filter").get_by_role("button", name="Apply").click()`</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr"/>
@@ -1258,17 +1193,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>H.10</t>
+          <t>H.5</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown icon again to open the filter condition options.</t>
+          <t>Click on the first 'Filter' button to open the filter configuration for the selected column.</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
+          <t>`page.get_by_title("Filter").first.click()`</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr"/>
@@ -1278,17 +1213,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>H.11</t>
+          <t>H.6</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Does not equal' option from the filter condition dropdown.</t>
+          <t>Click on the dropdown icon to open the filter condition options.</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Does not equal").click()`</t>
+          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr"/>
@@ -1298,17 +1233,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>H.12</t>
+          <t>H.7</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown icon again to open the filter condition options.</t>
+          <t>Select the 'Does not contain' option from the filter condition dropdown.</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
+          <t>`page.get_by_role("option", name="Does not contain").click()`</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr"/>
@@ -1318,17 +1253,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>H.13</t>
+          <t>H.8</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Begins with' option from the filter condition dropdown.</t>
+          <t>Click on the dropdown icon again to open the filter condition options.</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Begins with").click()`</t>
+          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
@@ -1338,17 +1273,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>H.14</t>
+          <t>H.9</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown icon again to open the filter condition options.</t>
+          <t>Select the 'Equals' option from the filter condition dropdown.</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
+          <t>`page.get_by_role("option", name="Equals").click()`</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr"/>
@@ -1358,17 +1293,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>H.15</t>
+          <t>H.10</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Ends with' option from the filter condition dropdown.</t>
+          <t>Click on the dropdown icon again to open the filter condition options.</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Ends with").click()`</t>
+          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr"/>
@@ -1378,17 +1313,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>H.16</t>
+          <t>H.11</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown icon again to open the filter condition options.</t>
+          <t>Select the 'Does not equal' option from the filter condition dropdown.</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
+          <t>`page.get_by_role("option", name="Does not equal").click()`</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
@@ -1398,17 +1333,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>H.17</t>
+          <t>H.12</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Does not contain' option from the filter condition dropdown again.</t>
+          <t>Click on the dropdown icon again to open the filter condition options.</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("option", name="Does not contain").click()`</t>
+          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr"/>
@@ -1418,17 +1353,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>H.18</t>
+          <t>H.13</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply' button to apply the selected filter condition.</t>
+          <t>Select the 'Begins with' option from the filter condition dropdown.</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("Column Filter").get_by_role("button", name="Apply").click()`</t>
+          <t>`page.get_by_role("option", name="Begins with").click()`</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr"/>
@@ -1438,17 +1373,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>H.19</t>
+          <t>H.14</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Click on the first 'Filter' button to reopen the filter configuration.</t>
+          <t>Click on the dropdown icon again to open the filter condition options.</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_title("Filter").first.click()`</t>
+          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
@@ -1458,17 +1393,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>H.20</t>
+          <t>H.15</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Reset' button to clear the applied filter and reset the filter configuration.</t>
+          <t>Select the 'Ends with' option from the filter condition dropdown.</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Reset").click()`</t>
+          <t>`page.get_by_role("option", name="Ends with").click()`</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr"/>
@@ -1478,17 +1413,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>I.1</t>
+          <t>H.16</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Click on the first pagination link to navigate to the first page of the table.</t>
+          <t>Click on the dropdown icon again to open the filter condition options.</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("a").first.click()`</t>
+          <t>`page.locator(".ag-icon.ag-icon-small-down").first.click()`</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr"/>
@@ -1498,17 +1433,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>I.2</t>
+          <t>H.17</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Click on the second pagination link to navigate to the second page of the table.</t>
+          <t>Select the 'Does not contain' option from the filter condition dropdown again.</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("a").nth(1).click()`</t>
+          <t>`page.get_by_role("option", name="Does not contain").click()`</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr"/>
@@ -1518,17 +1453,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>I.3</t>
+          <t>H.18</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Next' button to navigate to the next page in the pagination.</t>
+          <t>Click on the 'Apply' button to apply the selected filter condition.</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".pagination-next &gt; .zeb-chevron-right").first.click()`</t>
+          <t>`page.get_by_label("Column Filter").get_by_role("button", name="Apply").click()`</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr"/>
@@ -1538,17 +1473,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>I.4</t>
+          <t>H.19</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Previous' button to navigate to the previous page in the pagination.</t>
+          <t>Click on the first 'Filter' button to reopen the filter configuration.</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".zeb-chevron-left").first.click()`</t>
+          <t>`page.get_by_title("Filter").first.click()`</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr"/>
@@ -1558,17 +1493,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>I.5</t>
+          <t>H.20</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'First' button to navigate to the first page in the pagination.</t>
+          <t>Click on the 'Reset' button to clear the applied filter and reset the filter configuration.</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".zeb-nav-to-first").first.click()`</t>
+          <t>`page.get_by_role("button", name="Reset").click()`</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr"/>
@@ -1576,39 +1511,26 @@
       <c r="F56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>J.1</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>Click on the dropdown to open the row view options.</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".d-flex &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").first.click()`</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="4" t="inlineStr"/>
-      <c r="F57" s="4" t="inlineStr"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>--- PAGINATION INTERACTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>J.2</t>
+          <t>I.1</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Select the option to view 20 rows per page from the dropdown menu.</t>
+          <t>Click on the first pagination link to navigate to the first page of the table.</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^View 20 row\(s\)$")).first.click()`</t>
+          <t>`page.locator("a").first.click()`</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr"/>
@@ -1618,17 +1540,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>J.3</t>
+          <t>I.2</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown again to open the row view options.</t>
+          <t>Click on the second pagination link to navigate to the second page of the table.</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").first.click()`</t>
+          <t>`page.locator("a").nth(1).click()`</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr"/>
@@ -1638,17 +1560,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>J.4</t>
+          <t>I.3</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Select the option to view 50 rows per page from the dropdown menu.</t>
+          <t>Click on the 'Next' button to navigate to the next page in the pagination.</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^View 50 row\(s\)$")).first.click()`</t>
+          <t>`page.locator(".pagination-next &gt; .zeb-chevron-right").first.click()`</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr"/>
@@ -1658,17 +1580,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>J.5</t>
+          <t>I.4</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown again to open the row view options.</t>
+          <t>Click on the 'Previous' button to navigate to the previous page in the pagination.</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").first.click()`</t>
+          <t>`page.locator(".zeb-chevron-left").first.click()`</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
@@ -1678,17 +1600,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>J.6</t>
+          <t>I.5</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Select the option to view 10 rows per page from the dropdown menu.</t>
+          <t>Click on the 'First' button to navigate to the first page in the pagination.</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^View 10 row\(s\)$")).nth(1).click()`</t>
+          <t>`page.locator(".zeb-nav-to-first").first.click()`</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr"/>
@@ -1696,39 +1618,26 @@
       <c r="F62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>J.7</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>Click on the text displaying the current row count and total rows to view detailed information.</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Locations 20 rows out of 968").click()`</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr"/>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="4" t="inlineStr"/>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>--- ROW VIEW OPTIONS ---</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>K.1</t>
+          <t>J.1</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Click on the right-facing chevron icon to expand the collapsed section.</t>
+          <t>Click on the dropdown to open the row view options.</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".pointer.chevron.zeb-chevron-right.m-r-12.collapsed").click()`</t>
+          <t>`page.locator(".d-flex &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").first.click()`</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr"/>
@@ -1738,17 +1647,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>K.2</t>
+          <t>J.2</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Locations" tab to navigate to the Locations section.</t>
+          <t>Select the option to view 20 rows per page from the dropdown menu.</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Locations", exact=True).click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^View 20 row\(s\)$")).first.click()`</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr"/>
@@ -1758,17 +1667,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>K.3</t>
+          <t>J.3</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the checkbox in the row labeled "Location" to deselect it.</t>
+          <t>Click on the dropdown again to open the row view options.</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("row", name="Location").get_by_role("checkbox").uncheck()`</t>
+          <t>`page.locator(".d-flex &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").first.click()`</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr"/>
@@ -1778,17 +1687,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>K.4</t>
+          <t>J.4</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Columns" button to open the column visibility options.</t>
+          <t>Select the option to view 50 rows per page from the dropdown menu.</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="columns").nth(1).click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^View 50 row\(s\)$")).first.click()`</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr"/>
@@ -1798,17 +1707,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>K.5</t>
+          <t>J.5</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the "Toggle All Columns Visibility" checkbox to hide all columns.</t>
+          <t>Click on the dropdown again to open the row view options.</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
+          <t>`page.locator(".d-flex &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").first.click()`</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr"/>
@@ -1818,17 +1727,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>K.6</t>
+          <t>J.6</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Check the "Store Count Column" checkbox to make the Store Count column visible.</t>
+          <t>Select the option to view 10 rows per page from the dropdown menu.</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Store Count Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^View 10 row\(s\)$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr"/>
@@ -1838,17 +1747,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>K.7</t>
+          <t>J.7</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Check the "Product Count Column" checkbox to make the Product Count column visible.</t>
+          <t>Click on the text displaying the current row count and total rows to view detailed information.</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Product Count Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_text("Locations 20 rows out of 968").click()`</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr"/>
@@ -1856,39 +1765,26 @@
       <c r="F70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>K.8</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>Check the "13W-Fcst Column" checkbox to make the 13W-Fcst column visible.</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("treeitem", name="13W-Fcst Column").get_by_label("Press SPACE to toggle").check()`</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr"/>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>--- LOCATION AND COLUMN VISIBILITY ---</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>K.9</t>
+          <t>K.1</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Filter Columns Input" textbox to activate it for typing.</t>
+          <t>Click on the right-facing chevron icon to expand the collapsed section.</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
+          <t>`page.locator(".pointer.chevron.zeb-chevron-right.m-r-12.collapsed").click()`</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr"/>
@@ -1898,17 +1794,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>K.10</t>
+          <t>K.2</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Type "Pre" into the "Filter Columns Input" textbox to filter the column list.</t>
+          <t>Click on the "Locations" tab to navigate to the Locations section.</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("Pre")`</t>
+          <t>`page.get_by_text("Locations", exact=True).click()`</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr"/>
@@ -1918,17 +1814,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>K.11</t>
+          <t>K.3</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Check the filtered checkbox labeled "Press SPACE to toggle" to make the column visible.</t>
+          <t>Uncheck the checkbox in the row labeled "Location" to deselect it.</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Press SPACE to toggle").check()`</t>
+          <t>`page.get_by_role("row", name="Location").get_by_role("checkbox").uncheck()`</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr"/>
@@ -1938,12 +1834,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>K.12</t>
+          <t>K.4</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Columns" button again to close the column visibility options.</t>
+          <t>Click on the "Columns" button to open the column visibility options.</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -1958,17 +1854,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>L.1</t>
+          <t>K.5</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Click on the filter icon located in the column header to open the column menu.</t>
+          <t>Uncheck the "Toggle All Columns Visibility" checkbox to hide all columns.</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#ag-header-cell-menu-button &gt; .filter-icon").click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr"/>
@@ -1978,17 +1874,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>L.2</t>
+          <t>K.6</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Filter Value" textbox to activate it for typing.</t>
+          <t>Check the "Store Count Column" checkbox to make the Store Count column visible.</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Value").click()`</t>
+          <t>`page.get_by_role("treeitem", name="Store Count Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr"/>
@@ -1998,17 +1894,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>L.3</t>
+          <t>K.7</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Type "CHICAGO" into the "Filter Value" textbox to filter the rows.</t>
+          <t>Check the "Product Count Column" checkbox to make the Product Count column visible.</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Filter Value").fill("CHICAGO")`</t>
+          <t>`page.get_by_role("treeitem", name="Product Count Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr"/>
@@ -2018,17 +1914,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>L.4</t>
+          <t>K.8</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Apply" button in the column menu to apply the filter.</t>
+          <t>Check the "13W-Fcst Column" checkbox to make the 13W-Fcst column visible.</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("Column Menu").get_by_role("button", name="Apply").click()`</t>
+          <t>`page.get_by_role("treeitem", name="13W-Fcst Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr"/>
@@ -2038,17 +1934,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>L.5</t>
+          <t>K.9</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox in the grid cell labeled "00162-1554 E 55TH ST-CHICAGO-" to select the row.</t>
+          <t>Click on the "Filter Columns Input" textbox to activate it for typing.</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("gridcell", name="00162-1554 E 55TH ST-CHICAGO-").get_by_role("checkbox").check()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").click()`</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr"/>
@@ -2058,17 +1954,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>L.6</t>
+          <t>K.10</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Click on the filter icon in the column header again to reopen the column menu.</t>
+          <t>Type "Pre" into the "Filter Columns Input" textbox to filter the column list.</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#ag-header-cell-menu-button &gt; .filter-icon").click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Columns Input").fill("Pre")`</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr"/>
@@ -2078,17 +1974,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>L.7</t>
+          <t>K.11</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Reset" button in the column menu to clear the applied filter.</t>
+          <t>Check the filtered checkbox labeled "Press SPACE to toggle" to make the column visible.</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("Column Menu").get_by_role("button", name="Reset").click()`</t>
+          <t>`page.get_by_role("checkbox", name="Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr"/>
@@ -2098,17 +1994,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>M.1</t>
+          <t>K.12</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Select the checkbox in the row labeled "Location" to mark it for pagination testing.</t>
+          <t>Click on the "Columns" button again to close the column visibility options.</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("row", name="Location").get_by_role("checkbox").check()`</t>
+          <t>`page.get_by_role("button", name="columns").nth(1).click()`</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr"/>
@@ -2116,39 +2012,26 @@
       <c r="F83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>M.2</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>Click on the page number "2" link to navigate to the second page of results.</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("a").filter(has_text="2").nth(1).click()`</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr"/>
-      <c r="E84" s="4" t="inlineStr"/>
-      <c r="F84" s="4" t="inlineStr"/>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>--- COLUMN MENU FILTERING ---</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>M.3</t>
+          <t>L.1</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Click on the page number "3" link to navigate to the third page of results.</t>
+          <t>Click on the filter icon located in the column header to open the column menu.</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("a").filter(has_text="3").nth(1).click()`</t>
+          <t>`page.locator("#ag-header-cell-menu-button &gt; .filter-icon").click()`</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr"/>
@@ -2158,17 +2041,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>M.4</t>
+          <t>L.2</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Next" button (right arrow) to move to the next page of results.</t>
+          <t>Click on the "Filter Value" textbox to activate it for typing.</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; esp-pagination-v2 &gt; .d-flex.w-100 &gt; .pagination-pager &gt; .pagination-next &gt; .zeb-chevron-right").click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Value").click()`</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr"/>
@@ -2178,17 +2061,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>M.5</t>
+          <t>L.3</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Previous" button (left arrow) to return to the previous page of results.</t>
+          <t>Type "CHICAGO" into the "Filter Value" textbox to filter the rows.</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; esp-pagination-v2 &gt; .d-flex.w-100 &gt; .pagination-pager &gt; .pagination-previous &gt; .zeb-chevron-left").click()`</t>
+          <t>`page.get_by_role("textbox", name="Filter Value").fill("CHICAGO")`</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr"/>
@@ -2198,17 +2081,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>M.6</t>
+          <t>L.4</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Click on the "First" button to navigate back to the first page of results.</t>
+          <t>Click on the "Apply" button in the column menu to apply the filter.</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; esp-pagination-v2 &gt; .d-flex.w-100 &gt; .pagination-pager &gt; .pagination-first &gt; .zeb-nav-to-first").click()`</t>
+          <t>`page.get_by_label("Column Menu").get_by_role("button", name="Apply").click()`</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr"/>
@@ -2218,17 +2101,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>N.1</t>
+          <t>L.5</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Filter' button to expand the filter options.</t>
+          <t>Check the checkbox in the grid cell labeled "00162-1554 E 55TH ST-CHICAGO-" to select the row.</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Filter").nth(2).click()`</t>
+          <t>`page.get_by_role("gridcell", name="00162-1554 E 55TH ST-CHICAGO-").get_by_role("checkbox").check()`</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr"/>
@@ -2238,17 +2121,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>N.2</t>
+          <t>L.6</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown for the 'Time' filter to view available time range options.</t>
+          <t>Click on the filter icon in the column header again to reopen the column menu.</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator("#ag-header-cell-menu-button &gt; .filter-icon").click()`</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr"/>
@@ -2258,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>N.3</t>
+          <t>L.7</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 4 Next 4' option from the 'Time' filter dropdown.</t>
+          <t>Click on the "Reset" button in the column menu to clear the applied filter.</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 4 Next 4$")).nth(1).click()`</t>
+          <t>`page.get_by_label("Column Menu").get_by_role("button", name="Reset").click()`</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr"/>
@@ -2276,39 +2159,26 @@
       <c r="F91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>N.4</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>Click on the dropdown for the 'Time' filter again to change the selection.</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr"/>
-      <c r="E92" s="4" t="inlineStr"/>
-      <c r="F92" s="4" t="inlineStr"/>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>--- PAGINATION NAVIGATION ---</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>N.5</t>
+          <t>M.1</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 4 Next 13' option from the 'Time' filter dropdown.</t>
+          <t>Select the checkbox in the row labeled "Location" to mark it for pagination testing.</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 4 Next 13$")).nth(1).click()`</t>
+          <t>`page.get_by_role("row", name="Location").get_by_role("checkbox").check()`</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr"/>
@@ -2318,17 +2188,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>N.6</t>
+          <t>M.2</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown for the 'Time' filter again to change the selection.</t>
+          <t>Click on the page number "2" link to navigate to the second page of results.</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator("a").filter(has_text="2").nth(1).click()`</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr"/>
@@ -2338,17 +2208,17 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>N.7</t>
+          <t>M.3</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 13 Next 13' option from the 'Time' filter dropdown.</t>
+          <t>Click on the page number "3" link to navigate to the third page of results.</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 13 Next 13$")).nth(1).click()`</t>
+          <t>`page.locator("a").filter(has_text="3").nth(1).click()`</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr"/>
@@ -2358,17 +2228,17 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>N.8</t>
+          <t>M.4</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown for the 'Time' filter again to change the selection.</t>
+          <t>Click on the "Next" button (right arrow) to move to the next page of results.</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator("div:nth-child(3) &gt; esp-pagination-v2 &gt; .d-flex.w-100 &gt; .pagination-pager &gt; .pagination-next &gt; .zeb-chevron-right").click()`</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr"/>
@@ -2378,17 +2248,17 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>N.9</t>
+          <t>M.5</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 52 Next 52' option from the 'Time' filter dropdown.</t>
+          <t>Click on the "Previous" button (left arrow) to return to the previous page of results.</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 52 Next 52$")).first.click()`</t>
+          <t>`page.locator("div:nth-child(3) &gt; esp-pagination-v2 &gt; .d-flex.w-100 &gt; .pagination-pager &gt; .pagination-previous &gt; .zeb-chevron-left").click()`</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr"/>
@@ -2398,17 +2268,17 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>N.10</t>
+          <t>M.6</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown for the 'Time' filter again to change the selection.</t>
+          <t>Click on the "First" button to navigate back to the first page of results.</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator("div:nth-child(3) &gt; esp-pagination-v2 &gt; .d-flex.w-100 &gt; .pagination-pager &gt; .pagination-first &gt; .zeb-nav-to-first").click()`</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr"/>
@@ -2416,39 +2286,26 @@
       <c r="F98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>N.11</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>Select the 'Latest 104 Next 52' option from the 'Time' filter dropdown.</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 104 Next 52$")).nth(1).click()`</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr"/>
-      <c r="E99" s="4" t="inlineStr"/>
-      <c r="F99" s="4" t="inlineStr"/>
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>--- TIME FILTER INTERACTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>N.12</t>
+          <t>N.1</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown for the 'Time' filter again to reset the selection.</t>
+          <t>Click on the 'Filter' button to expand the filter options.</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.get_by_text("Filter").nth(2).click()`</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr"/>
@@ -2458,17 +2315,17 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>N.13</t>
+          <t>N.2</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Latest 4 Next 4' option from the 'Time' filter dropdown to reset the filter.</t>
+          <t>Click on the dropdown for the 'Time' filter to view available time range options.</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 4 Next 4$")).nth(1).click()`</t>
+          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr"/>
@@ -2478,17 +2335,17 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>O.1</t>
+          <t>N.3</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown for the 'Event' filter to view available event options.</t>
+          <t>Select the 'Latest 4 Next 4' option from the 'Time' filter dropdown.</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#event-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 4 Next 4$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr"/>
@@ -2498,17 +2355,17 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>O.2</t>
+          <t>N.4</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list to expand the filter options.</t>
+          <t>Click on the dropdown for the 'Time' filter again to change the selection.</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr"/>
@@ -2518,17 +2375,17 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>O.3</t>
+          <t>N.5</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Search' textbox to focus on it.</t>
+          <t>Select the 'Latest 4 Next 13' option from the 'Time' filter dropdown.</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Search").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 4 Next 13$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr"/>
@@ -2538,17 +2395,17 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>O.4</t>
+          <t>N.6</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Fill the 'Search' textbox with the value 'TLC'.</t>
+          <t>Click on the dropdown for the 'Time' filter again to change the selection.</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Search").fill("TLC")`</t>
+          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr"/>
@@ -2558,17 +2415,17 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>O.5</t>
+          <t>N.7</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Click on the close icon to clear the search input.</t>
+          <t>Select the 'Latest 13 Next 13' option from the 'Time' filter dropdown.</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".icon.d-flex.pointer.zeb-close").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 13 Next 13$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr"/>
@@ -2578,17 +2435,17 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>P.1</t>
+          <t>N.8</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret for the 'Ad Location' filter to expand the options.</t>
+          <t>Click on the dropdown for the 'Time' filter again to change the selection.</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".not-allowed &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").first.click()`</t>
+          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr"/>
@@ -2598,17 +2455,17 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>P.2</t>
+          <t>N.9</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret for the 'Ad Location' filter again to view the options.</t>
+          <t>Select the 'Latest 52 Next 52' option from the 'Time' filter dropdown.</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#ad-location-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 52 Next 52$")).first.click()`</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr"/>
@@ -2618,17 +2475,17 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>P.3</t>
+          <t>N.10</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list to expand the filter options.</t>
+          <t>Click on the dropdown for the 'Time' filter again to change the selection.</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr"/>
@@ -2638,17 +2495,17 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>P.4</t>
+          <t>N.11</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list again to confirm the selection.</t>
+          <t>Select the 'Latest 104 Next 52' option from the 'Time' filter dropdown.</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 104 Next 52$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr"/>
@@ -2658,17 +2515,17 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>P.5</t>
+          <t>N.12</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret for the 'Ad Location' filter to collapse the options.</t>
+          <t>Click on the dropdown for the 'Time' filter again to reset the selection.</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#ad-location-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator("#time-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr"/>
@@ -2678,17 +2535,17 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>Q.1</t>
+          <t>N.13</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret for the 'Segment' filter to expand the options.</t>
+          <t>Select the 'Latest 4 Next 4' option from the 'Time' filter dropdown to reset the filter.</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#segment-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Latest 4 Next 4$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr"/>
@@ -2696,39 +2553,26 @@
       <c r="F112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>Q.2</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>Click on the first element in the list to expand the filter options.</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr"/>
-      <c r="E113" s="4" t="inlineStr"/>
-      <c r="F113" s="4" t="inlineStr"/>
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>--- EVENT FILTER INTERACTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>Q.3</t>
+          <t>O.1</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list again to confirm the selection.</t>
+          <t>Click on the dropdown for the 'Event' filter to view available event options.</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator("#event-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr"/>
@@ -2738,17 +2582,17 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Q.4</t>
+          <t>O.2</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret for the 'Segment' filter to collapse the options.</t>
+          <t>Click on the first element in the list to expand the filter options.</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#segment-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr"/>
@@ -2758,17 +2602,17 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>R.1</t>
+          <t>O.3</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown for the 'Vendor' filter to expand the options.</t>
+          <t>Click on the 'Search' textbox to focus on it.</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#vendor-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100").click()`</t>
+          <t>`page.get_by_role("textbox", name="Search").click()`</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr"/>
@@ -2778,17 +2622,17 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>R.2</t>
+          <t>O.4</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list to expand the filter options.</t>
+          <t>Fill the 'Search' textbox with the value 'TLC'.</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.get_by_role("textbox", name="Search").fill("TLC")`</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr"/>
@@ -2798,17 +2642,17 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>R.3</t>
+          <t>O.5</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Click on the first option in the 'Vendor' filter dropdown to select it.</t>
+          <t>Click on the close icon to clear the search input.</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
+          <t>`page.locator(".icon.d-flex.pointer.zeb-close").click()`</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr"/>
@@ -2816,39 +2660,26 @@
       <c r="F118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>R.4</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>Click on the second option in the 'Vendor' filter dropdown to select it.</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(2) &gt; .d-flex").click()`</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr"/>
-      <c r="E119" s="4" t="inlineStr"/>
-      <c r="F119" s="4" t="inlineStr"/>
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>--- AD LOCATION FILTER INTERACTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>R.5</t>
+          <t>P.1</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list again to confirm the selection.</t>
+          <t>Click on the dropdown caret for the 'Ad Location' filter to expand the options.</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator(".not-allowed &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").first.click()`</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr"/>
@@ -2858,17 +2689,17 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>R.6</t>
+          <t>P.2</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret for the 'Vendor' filter again to view the options.</t>
+          <t>Click on the dropdown caret for the 'Ad Location' filter again to view the options.</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#vendor-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator("#ad-location-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr"/>
@@ -2878,17 +2709,17 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>R.7</t>
+          <t>P.3</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply' button to apply the selected filters.</t>
+          <t>Click on the first element in the list to expand the filter options.</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("button").filter(has_text=re.compile(r"^Apply$")).click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr"/>
@@ -2898,17 +2729,17 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>S.1</t>
+          <t>P.4</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret to expand the column visibility options.</t>
+          <t>Click on the first element in the list again to confirm the selection.</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ellipses &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr"/>
@@ -2918,17 +2749,17 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>S.2</t>
+          <t>P.5</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list to expand the filter options.</t>
+          <t>Click on the dropdown caret for the 'Ad Location' filter to collapse the options.</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator("#ad-location-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr"/>
@@ -2936,39 +2767,26 @@
       <c r="F124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>S.3</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
-        <is>
-          <t>Select the first checkbox to make the corresponding column visible.</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr"/>
-      <c r="E125" s="4" t="inlineStr"/>
-      <c r="F125" s="4" t="inlineStr"/>
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>--- SEGMENT FILTER INTERACTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>S.4</t>
+          <t>Q.1</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>Select the second checkbox to make the corresponding column visible.</t>
+          <t>Click on the dropdown caret for the 'Segment' filter to expand the options.</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
+          <t>`page.locator("#segment-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr"/>
@@ -2978,17 +2796,17 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>S.5</t>
+          <t>Q.2</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Select the third checkbox to make the corresponding column visible.</t>
+          <t>Click on the first element in the list to expand the filter options.</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr"/>
@@ -2998,17 +2816,17 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>S.6</t>
+          <t>Q.3</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Select the fourth checkbox to make the corresponding column visible.</t>
+          <t>Click on the first element in the list again to confirm the selection.</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr"/>
@@ -3018,17 +2836,17 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>S.7</t>
+          <t>Q.4</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list again to confirm the selection.</t>
+          <t>Click on the dropdown caret for the 'Segment' filter to collapse the options.</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator("#segment-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr"/>
@@ -3036,39 +2854,26 @@
       <c r="F129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>S.8</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>Deselect the first checkbox to hide the corresponding column.</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.deselected").first.click()`</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="inlineStr"/>
-      <c r="E130" s="4" t="inlineStr"/>
-      <c r="F130" s="4" t="inlineStr"/>
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>--- VENDOR FILTER INTERACTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>S.9</t>
+          <t>R.1</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Deselect the second checkbox to hide the corresponding column.</t>
+          <t>Click on the dropdown for the 'Vendor' filter to expand the options.</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.deselected").first.click()`</t>
+          <t>`page.locator("#vendor-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100").click()`</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr"/>
@@ -3078,17 +2883,17 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>S.10</t>
+          <t>R.2</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>Deselect the third checkbox to hide the corresponding column.</t>
+          <t>Click on the first element in the list to expand the filter options.</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.deselected").first.click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr"/>
@@ -3098,17 +2903,17 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>S.11</t>
+          <t>R.3</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Click on the fifth element in the list to select a specific column.</t>
+          <t>Click on the first option in the 'Vendor' filter dropdown to select it.</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(5)").click()`</t>
+          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr"/>
@@ -3118,17 +2923,17 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>S.12</t>
+          <t>R.4</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret again to collapse the column visibility options.</t>
+          <t>Click on the second option in the 'Vendor' filter dropdown to select it.</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ellipses &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(2) &gt; .d-flex").click()`</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr"/>
@@ -3138,17 +2943,17 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>S.13</t>
+          <t>R.5</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret for another section to expand its options.</t>
+          <t>Click on the first element in the list again to confirm the selection.</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr"/>
@@ -3158,17 +2963,17 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>S.14</t>
+          <t>R.6</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list to expand the filter options.</t>
+          <t>Click on the dropdown caret for the 'Vendor' filter again to view the options.</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator("#vendor-filterId &gt; .wr-20 &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr"/>
@@ -3178,17 +2983,17 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>S.15</t>
+          <t>R.7</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list again to confirm the selection.</t>
+          <t>Click on the 'Apply' button to apply the selected filters.</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator("button").filter(has_text=re.compile(r"^Apply$")).click()`</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr"/>
@@ -3196,39 +3001,26 @@
       <c r="F137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="inlineStr">
-        <is>
-          <t>S.16</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="inlineStr">
-        <is>
-          <t>Click on the dropdown caret for another section again to collapse its options.</t>
-        </is>
-      </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
-        </is>
-      </c>
-      <c r="D138" s="3" t="inlineStr"/>
-      <c r="E138" s="4" t="inlineStr"/>
-      <c r="F138" s="4" t="inlineStr"/>
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>--- COLUMN VISIBILITY OPTIONS ---</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>S.17</t>
+          <t>S.1</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Columns' button to open the column visibility settings.</t>
+          <t>Click on the dropdown caret to expand the column visibility options.</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="columns").nth(2).click()`</t>
+          <t>`page.locator(".ellipses &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr"/>
@@ -3238,17 +3030,17 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>S.18</t>
+          <t>S.2</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to deselect all columns.</t>
+          <t>Click on the first element in the list to expand the filter options.</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr"/>
@@ -3258,17 +3050,17 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>S.19</t>
+          <t>S.3</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Click on the first column in the list to make it visible.</t>
+          <t>Select the first checkbox to make the corresponding column visible.</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#ag-6720 &gt; .ag-column-panel &gt; .ag-column-select &gt; .ag-column-select-list &gt; .ag-virtual-list-viewport &gt; .ag-virtual-list-container &gt; div &gt; .ag-column-select-column").first.click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr"/>
@@ -3278,17 +3070,17 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>S.20</t>
+          <t>S.4</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the '/11/2026 Column' to make it visible.</t>
+          <t>Select the second checkbox to make the corresponding column visible.</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="/11/2026 Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr"/>
@@ -3298,17 +3090,17 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>S.21</t>
+          <t>S.5</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the '/18/2026 Column' to make it visible.</t>
+          <t>Select the third checkbox to make the corresponding column visible.</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="/18/2026 Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr"/>
@@ -3318,17 +3110,17 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>S.22</t>
+          <t>S.6</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the '/25/2026 Column' to make it visible.</t>
+          <t>Select the fourth checkbox to make the corresponding column visible.</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="/25/2026 Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr"/>
@@ -3338,17 +3130,17 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>S.23</t>
+          <t>S.7</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the '02/01/2026 Column' to make it visible.</t>
+          <t>Click on the first element in the list again to confirm the selection.</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="02/01/2026 Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr"/>
@@ -3358,17 +3150,17 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>S.24</t>
+          <t>S.8</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the '/08/2026 Column' to make it visible.</t>
+          <t>Deselect the first checkbox to hide the corresponding column.</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="/08/2026 Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.deselected").first.click()`</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr"/>
@@ -3378,17 +3170,17 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>S.25</t>
+          <t>S.9</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Toggle All Columns Visibility' checkbox to select all columns.</t>
+          <t>Deselect the second checkbox to hide the corresponding column.</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.deselected").first.click()`</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr"/>
@@ -3398,17 +3190,17 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>S.26</t>
+          <t>S.10</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Columns' button again to close the column visibility settings.</t>
+          <t>Deselect the third checkbox to hide the corresponding column.</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="columns").nth(2).click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.deselected").first.click()`</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr"/>
@@ -3418,17 +3210,17 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>T.1</t>
+          <t>S.11</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret to expand the additional column visibility options.</t>
+          <t>Click on the fifth element in the list to select a specific column.</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(5)").click()`</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr"/>
@@ -3438,17 +3230,17 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>T.2</t>
+          <t>S.12</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list to expand the filter options.</t>
+          <t>Click on the dropdown caret again to collapse the column visibility options.</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator(".ellipses &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr"/>
@@ -3458,17 +3250,17 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>T.3</t>
+          <t>S.13</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Click on the first element in the list again to confirm the selection.</t>
+          <t>Click on the dropdown caret for another section to expand its options.</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr"/>
@@ -3478,17 +3270,17 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>T.4</t>
+          <t>S.14</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>Click on the first dropdown option to select it.</t>
+          <t>Click on the first element in the list to expand the filter options.</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr"/>
@@ -3498,17 +3290,17 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>T.5</t>
+          <t>S.15</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Click on the first dropdown option again to confirm the selection.</t>
+          <t>Click on the first element in the list again to confirm the selection.</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr"/>
@@ -3518,17 +3310,17 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>T.6</t>
+          <t>S.16</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Click on the first dropdown option once more to finalize the selection.</t>
+          <t>Click on the dropdown caret for another section again to collapse its options.</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
+          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr"/>
@@ -3538,17 +3330,17 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>T.7</t>
+          <t>S.17</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Click on the fourth element in the list to select a specific column.</t>
+          <t>Click on the 'Columns' button to open the column visibility settings.</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(4) &gt; .d-flex").click()`</t>
+          <t>`page.get_by_role("button", name="columns").nth(2).click()`</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr"/>
@@ -3558,17 +3350,17 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>T.8</t>
+          <t>S.18</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Click on the fifth element in the list to select another specific column.</t>
+          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to deselect all columns.</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(5) &gt; .d-flex").click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr"/>
@@ -3578,17 +3370,17 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>T.9</t>
+          <t>S.19</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Maximum User Forecast" option to select it.</t>
+          <t>Click on the first column in the list to make it visible.</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Maximum User Forecast").nth(1).click()`</t>
+          <t>`page.locator("#ag-6720 &gt; .ag-column-panel &gt; .ag-column-select &gt; .ag-column-select-list &gt; .ag-virtual-list-viewport &gt; .ag-virtual-list-container &gt; div &gt; .ag-column-select-column").first.click()`</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr"/>
@@ -3598,17 +3390,17 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>T.10</t>
+          <t>S.20</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Average User Forecast" option to select it.</t>
+          <t>Check the checkbox for the '/11/2026 Column' to make it visible.</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Average User Forecast").nth(1).click()`</t>
+          <t>`page.get_by_role("treeitem", name="/11/2026 Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr"/>
@@ -3618,17 +3410,17 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>T.11</t>
+          <t>S.21</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Click on the eighth element in the list to select another specific column.</t>
+          <t>Check the checkbox for the '/18/2026 Column' to make it visible.</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".overflow-auto &gt; div:nth-child(8)").click()`</t>
+          <t>`page.get_by_role("treeitem", name="/18/2026 Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr"/>
@@ -3638,17 +3430,17 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>T.12</t>
+          <t>S.22</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Click on the first dropdown option to finalize the selection.</t>
+          <t>Check the checkbox for the '/25/2026 Column' to make it visible.</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".d-flex.dropdown-option").first.click()`</t>
+          <t>`page.get_by_role("treeitem", name="/25/2026 Column").get_by_label("Press SPACE to toggle").check()`</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr"/>
@@ -3658,17 +3450,17 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>T.13</t>
+          <t>S.23</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown caret again to collapse the additional column visibility options.</t>
+          <t>Check the checkbox for the '02/01/2026 Column' to make it visible.</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+          <t>`page.get_by_role("treeitem", name="02/01/2026 Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr"/>
@@ -3678,17 +3470,17 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>T.14</t>
+          <t>S.24</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Click on the third element in the list to select a specific column.</t>
+          <t>Check the checkbox for the '/08/2026 Column' to make it visible.</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(3) &gt; span &gt; .align-middle").click()`</t>
+          <t>`page.get_by_role("treeitem", name="/08/2026 Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr"/>
@@ -3698,17 +3490,17 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>T.15</t>
+          <t>S.25</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Click on the filter icon in the header to open the filter settings.</t>
+          <t>Check the 'Toggle All Columns Visibility' checkbox to select all columns.</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".ag-header-cell.ag-header-parent-hidden.ag-header-cell-sortable.ag-header-background.ag-focus-managed.ag-header-active &gt; .ag-header-cell-comp-wrapper &gt; .ag-cell-label-container &gt; .ag-header-icon &gt; .filter-icon").click()`</t>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr"/>
@@ -3718,17 +3510,17 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>T.16</t>
+          <t>S.26</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Click on the "Apply" button in the filter settings to apply the changes.</t>
+          <t>Click on the 'Columns' button again to close the column visibility settings.</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_label("Column Filter").get_by_role("button", name="Apply").click()`</t>
+          <t>`page.get_by_role("button", name="columns").nth(2).click()`</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr"/>
@@ -3736,39 +3528,26 @@
       <c r="F164" s="4" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>T.17</t>
-        </is>
-      </c>
-      <c r="B165" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'Columns' button to open the column visibility settings.</t>
-        </is>
-      </c>
-      <c r="C165" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("button", name="columns").nth(3).click()`</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="inlineStr"/>
-      <c r="E165" s="4" t="inlineStr"/>
-      <c r="F165" s="4" t="inlineStr"/>
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>--- ADDITIONAL COLUMN VISIBILITY SETTINGS ---</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>T.18</t>
+          <t>T.1</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to deselect all columns.</t>
+          <t>Click on the dropdown caret to expand the additional column visibility options.</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
+          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr"/>
@@ -3778,17 +3557,17 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>T.19</t>
+          <t>T.2</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the 'Start Week Column' to make it visible.</t>
+          <t>Click on the first element in the list to expand the filter options.</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Start Week Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr"/>
@@ -3798,17 +3577,17 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>T.20</t>
+          <t>T.3</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the 'End Week Column' to make it visible.</t>
+          <t>Click on the first element in the list again to confirm the selection.</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="End Week Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr"/>
@@ -3818,17 +3597,17 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>T.21</t>
+          <t>T.4</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the 'Clone Column' to make it visible.</t>
+          <t>Click on the first dropdown option to select it.</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Clone Column").get_by_label("Press SPACE to toggle").check()`</t>
+          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr"/>
@@ -3838,17 +3617,17 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>T.22</t>
+          <t>T.5</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the 'Event Column' to make it visible.</t>
+          <t>Click on the first dropdown option again to confirm the selection.</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Event Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr"/>
@@ -3858,17 +3637,17 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>T.23</t>
+          <t>T.6</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the 'Market Column' to make it visible.</t>
+          <t>Click on the first dropdown option once more to finalize the selection.</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Market Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr"/>
@@ -3878,17 +3657,17 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>T.24</t>
+          <t>T.7</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the 'Count of Stores Column' to make it visible.</t>
+          <t>Click on the fourth element in the list to select a specific column.</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Count of Stores Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(4) &gt; .d-flex").click()`</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr"/>
@@ -3898,17 +3677,17 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>T.25</t>
+          <t>T.8</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the 'Spot Column' to make it visible.</t>
+          <t>Click on the fifth element in the list to select another specific column.</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("treeitem", name="Spot Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+          <t>`page.locator("div:nth-child(5) &gt; .d-flex").click()`</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr"/>
@@ -3918,17 +3697,17 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>T.26</t>
+          <t>T.9</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Check the 'Toggle All Columns Visibility' checkbox to select all columns.</t>
+          <t>Click on the "Maximum User Forecast" option to select it.</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
+          <t>`page.get_by_text("Maximum User Forecast").nth(1).click()`</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr"/>
@@ -3938,17 +3717,17 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>T.27</t>
+          <t>T.10</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Columns' button again to close the column visibility settings.</t>
+          <t>Click on the "Average User Forecast" option to select it.</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="columns").nth(3).click()`</t>
+          <t>`page.get_by_text("Average User Forecast").nth(1).click()`</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr"/>
@@ -3958,17 +3737,17 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>U.1</t>
+          <t>T.11</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Click on the page number "2" link to navigate to the second page of the results.</t>
+          <t>Click on the eighth element in the list to select another specific column.</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("a").filter(has_text="2").nth(2).click()`</t>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(8)").click()`</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr"/>
@@ -3978,17 +3757,17 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>U.2</t>
+          <t>T.12</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Click on the page number "3" link to navigate to the third page of the results.</t>
+          <t>Click on the first dropdown option to finalize the selection.</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("a").filter(has_text="3").nth(2).click()`</t>
+          <t>`page.locator(".d-flex.dropdown-option").first.click()`</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr"/>
@@ -3998,26 +3777,391 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>U.3</t>
+          <t>T.13</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Click on the "First Page" button in the pagination controls to navigate back to the first page of the results.</t>
+          <t>Click on the dropdown caret again to collapse the additional column visibility options.</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(7) &gt; div &gt; .componentParentWrapper &gt; esp-grid-container &gt; esp-card-component &gt; .card-container &gt; .card-content &gt; esp-row-dimentional-grid &gt; div &gt; #paginationId &gt; esp-pagination-v2 &gt; .d-flex.w-100 &gt; .pagination-pager &gt; .pagination-first").click()`</t>
+          <t>`page.locator(".wr-20.font-weight-normal &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr"/>
       <c r="E178" s="4" t="inlineStr"/>
       <c r="F178" s="4" t="inlineStr"/>
     </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>T.14</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>Click on the third element in the list to select a specific column.</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div:nth-child(3) &gt; span &gt; .align-middle").click()`</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr"/>
+      <c r="E179" s="4" t="inlineStr"/>
+      <c r="F179" s="4" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>T.15</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>Click on the filter icon in the header to open the filter settings.</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".ag-header-cell.ag-header-parent-hidden.ag-header-cell-sortable.ag-header-background.ag-focus-managed.ag-header-active &gt; .ag-header-cell-comp-wrapper &gt; .ag-cell-label-container &gt; .ag-header-icon &gt; .filter-icon").click()`</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr"/>
+      <c r="E180" s="4" t="inlineStr"/>
+      <c r="F180" s="4" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>T.16</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>Click on the "Apply" button in the filter settings to apply the changes.</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_label("Column Filter").get_by_role("button", name="Apply").click()`</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr"/>
+      <c r="E181" s="4" t="inlineStr"/>
+      <c r="F181" s="4" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>T.17</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Columns' button to open the column visibility settings.</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("button", name="columns").nth(3).click()`</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr"/>
+      <c r="E182" s="4" t="inlineStr"/>
+      <c r="F182" s="4" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>T.18</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>Uncheck the 'Toggle All Columns Visibility' checkbox to deselect all columns.</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").uncheck()`</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr"/>
+      <c r="E183" s="4" t="inlineStr"/>
+      <c r="F183" s="4" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>T.19</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>Check the checkbox for the 'Start Week Column' to make it visible.</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("treeitem", name="Start Week Column").get_by_label("Press SPACE to toggle").check()`</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr"/>
+      <c r="E184" s="4" t="inlineStr"/>
+      <c r="F184" s="4" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>T.20</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>Check the checkbox for the 'End Week Column' to make it visible.</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("treeitem", name="End Week Column").get_by_label("Press SPACE to toggle").check()`</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr"/>
+      <c r="E185" s="4" t="inlineStr"/>
+      <c r="F185" s="4" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>T.21</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>Check the checkbox for the 'Clone Column' to make it visible.</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("treeitem", name="Clone Column").get_by_label("Press SPACE to toggle").check()`</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr"/>
+      <c r="E186" s="4" t="inlineStr"/>
+      <c r="F186" s="4" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>T.22</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>Check the checkbox for the 'Event Column' to make it visible.</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("treeitem", name="Event Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr"/>
+      <c r="E187" s="4" t="inlineStr"/>
+      <c r="F187" s="4" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>T.23</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>Check the checkbox for the 'Market Column' to make it visible.</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("treeitem", name="Market Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr"/>
+      <c r="E188" s="4" t="inlineStr"/>
+      <c r="F188" s="4" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>T.24</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>Check the checkbox for the 'Count of Stores Column' to make it visible.</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("treeitem", name="Count of Stores Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr"/>
+      <c r="E189" s="4" t="inlineStr"/>
+      <c r="F189" s="4" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>T.25</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>Check the checkbox for the 'Spot Column' to make it visible.</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("treeitem", name="Spot Column").get_by_label("Press SPACE to toggle visibility (hidden)").check()`</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr"/>
+      <c r="E190" s="4" t="inlineStr"/>
+      <c r="F190" s="4" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>T.26</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>Check the 'Toggle All Columns Visibility' checkbox to select all columns.</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("checkbox", name="Toggle All Columns Visibility").check()`</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr"/>
+      <c r="E191" s="4" t="inlineStr"/>
+      <c r="F191" s="4" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>T.27</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Columns' button again to close the column visibility settings.</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("button", name="columns").nth(3).click()`</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr"/>
+      <c r="E192" s="4" t="inlineStr"/>
+      <c r="F192" s="4" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>--- FINAL PAGINATION NAVIGATION ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>U.1</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>Click on the page number "2" link to navigate to the second page of the results.</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("a").filter(has_text="2").nth(2).click()`</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr"/>
+      <c r="E194" s="4" t="inlineStr"/>
+      <c r="F194" s="4" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>U.2</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>Click on the page number "3" link to navigate to the third page of the results.</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("a").filter(has_text="3").nth(2).click()`</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr"/>
+      <c r="E195" s="4" t="inlineStr"/>
+      <c r="F195" s="4" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>U.3</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>Click on the "First Page" button in the pagination controls to navigate back to the first page of the results.</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div:nth-child(7) &gt; div &gt; .componentParentWrapper &gt; esp-grid-container &gt; esp-card-component &gt; .card-container &gt; .card-content &gt; esp-row-dimentional-grid &gt; div &gt; #paginationId &gt; esp-pagination-v2 &gt; .d-flex.w-100 &gt; .pagination-pager &gt; .pagination-first").click()`</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr"/>
+      <c r="E196" s="4" t="inlineStr"/>
+      <c r="F196" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="19">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A193:F193"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A165:F165"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A125:F125"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A130:F130"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A119:F119"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
